--- a/db/inflections/inflection_templates.xlsx
+++ b/db/inflections/inflection_templates.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10015" uniqueCount="2695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10015" uniqueCount="2693">
   <si>
     <t xml:space="preserve">inflection name</t>
   </si>
@@ -3301,7 +3301,8 @@
 ā</t>
   </si>
   <si>
-    <t xml:space="preserve">atī</t>
+    <t xml:space="preserve">atī
+antī</t>
   </si>
   <si>
     <t xml:space="preserve">atī
@@ -3380,7 +3381,8 @@
 ātu</t>
   </si>
   <si>
-    <t xml:space="preserve">atiṃ</t>
+    <t xml:space="preserve">atiṃ
+antiṃ</t>
   </si>
   <si>
     <t xml:space="preserve">atiyo
@@ -3438,7 +3440,8 @@
 ātha</t>
   </si>
   <si>
-    <t xml:space="preserve">atiyā</t>
+    <t xml:space="preserve">atiyā
+antiyā</t>
   </si>
   <si>
     <t xml:space="preserve">atīhi</t>
@@ -3615,7 +3618,8 @@
   </si>
   <si>
     <t xml:space="preserve">atiyaṃ
-atiyā</t>
+atiyā
+antiyaṃ antiyā</t>
   </si>
   <si>
     <t xml:space="preserve">atīsu</t>
@@ -3644,7 +3648,9 @@
   </si>
   <si>
     <t xml:space="preserve">ati
-atī</t>
+atī
+anti
+antī</t>
   </si>
   <si>
     <t xml:space="preserve">antāni
@@ -5649,10 +5655,6 @@
 ā</t>
   </si>
   <si>
-    <t xml:space="preserve">atī
-antī</t>
-  </si>
-  <si>
     <t xml:space="preserve">atiyo
 antiyo</t>
   </si>
@@ -5724,10 +5726,6 @@
   <si>
     <t xml:space="preserve">ante
 anto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">atiṃ
-antiṃ</t>
   </si>
   <si>
     <t xml:space="preserve">bhavantaṃ</t>
@@ -44834,7 +44832,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="54.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
         <v>599</v>
       </c>
@@ -45058,7 +45056,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="42.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="54.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
         <v>630</v>
       </c>
@@ -57300,25 +57298,25 @@
         <v>424</v>
       </c>
       <c r="F114" s="37" t="s">
-        <v>1603</v>
+        <v>983</v>
       </c>
       <c r="G114" s="49" t="s">
         <v>426</v>
       </c>
       <c r="H114" s="37" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="I114" s="49" t="s">
         <v>428</v>
       </c>
       <c r="J114" s="21" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="K114" s="48" t="s">
         <v>430</v>
       </c>
       <c r="L114" s="21" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="M114" s="48" t="s">
         <v>432</v>
@@ -57333,37 +57331,37 @@
         <v>420</v>
       </c>
       <c r="AD114" s="24" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="AE114" s="53" t="s">
         <v>422</v>
       </c>
       <c r="AF114" s="24" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="AG114" s="53" t="s">
         <v>424</v>
       </c>
       <c r="AH114" s="67" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="AI114" s="69" t="s">
         <v>426</v>
       </c>
       <c r="AJ114" s="67" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AK114" s="69" t="s">
         <v>428</v>
       </c>
       <c r="AL114" s="24" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AM114" s="53" t="s">
         <v>430</v>
       </c>
       <c r="AN114" s="24" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="AO114" s="53" t="s">
         <v>432</v>
@@ -57379,13 +57377,13 @@
         <v>420</v>
       </c>
       <c r="BF114" s="41" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="BG114" s="56" t="s">
         <v>422</v>
       </c>
       <c r="BH114" s="41" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="BI114" s="56" t="s">
         <v>424</v>
@@ -57394,13 +57392,13 @@
         <v>420</v>
       </c>
       <c r="BR114" s="76" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="BS114" s="78" t="s">
         <v>426</v>
       </c>
       <c r="BT114" s="76" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="BU114" s="78" t="s">
         <v>428</v>
@@ -57412,7 +57410,7 @@
         <v>736</v>
       </c>
       <c r="CJ114" s="59" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="CK114" s="60" t="s">
         <v>738</v>
@@ -57424,7 +57422,7 @@
         <v>740</v>
       </c>
       <c r="CN114" s="59" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="CO114" s="60" t="s">
         <v>978</v>
@@ -57439,25 +57437,25 @@
         <v>655</v>
       </c>
       <c r="CT114" s="70" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="CU114" s="71" t="s">
         <v>657</v>
       </c>
       <c r="CV114" s="70" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="CW114" s="71" t="s">
         <v>659</v>
       </c>
       <c r="CX114" s="70" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="CY114" s="71" t="s">
         <v>661</v>
       </c>
       <c r="CZ114" s="70" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="DA114" s="71" t="s">
         <v>663</v>
@@ -57474,31 +57472,31 @@
         <v>459</v>
       </c>
       <c r="D115" s="21" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="E115" s="48" t="s">
         <v>461</v>
       </c>
       <c r="F115" s="37" t="s">
-        <v>1624</v>
+        <v>1001</v>
       </c>
       <c r="G115" s="49" t="s">
         <v>462</v>
       </c>
       <c r="H115" s="37" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="I115" s="49" t="s">
         <v>463</v>
       </c>
       <c r="J115" s="21" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="K115" s="48" t="s">
         <v>464</v>
       </c>
       <c r="L115" s="21" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="M115" s="48" t="s">
         <v>466</v>
@@ -57513,37 +57511,37 @@
         <v>458</v>
       </c>
       <c r="AD115" s="24" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AE115" s="53" t="s">
         <v>459</v>
       </c>
       <c r="AF115" s="24" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="AG115" s="53" t="s">
         <v>461</v>
       </c>
       <c r="AH115" s="67" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AI115" s="69" t="s">
         <v>462</v>
       </c>
       <c r="AJ115" s="67" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="AK115" s="69" t="s">
         <v>463</v>
       </c>
       <c r="AL115" s="24" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="AM115" s="53" t="s">
         <v>464</v>
       </c>
       <c r="AN115" s="24" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="AO115" s="53" t="s">
         <v>466</v>
@@ -57559,13 +57557,13 @@
         <v>458</v>
       </c>
       <c r="BF115" s="41" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="BG115" s="56" t="s">
         <v>459</v>
       </c>
       <c r="BH115" s="41" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="BI115" s="56" t="s">
         <v>461</v>
@@ -57574,13 +57572,13 @@
         <v>458</v>
       </c>
       <c r="BR115" s="76" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="BS115" s="78" t="s">
         <v>462</v>
       </c>
       <c r="BT115" s="76" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="BU115" s="78" t="s">
         <v>463</v>
@@ -57601,25 +57599,25 @@
         <v>667</v>
       </c>
       <c r="CT115" s="46" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="CU115" s="19" t="s">
         <v>669</v>
       </c>
       <c r="CV115" s="46" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="CW115" s="19" t="s">
         <v>671</v>
       </c>
       <c r="CX115" s="46" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="CY115" s="19" t="s">
         <v>673</v>
       </c>
       <c r="CZ115" s="46" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="DA115" s="19" t="s">
         <v>675</v>
@@ -57642,19 +57640,19 @@
         <v>489</v>
       </c>
       <c r="F116" s="37" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="G116" s="49" t="s">
         <v>491</v>
       </c>
       <c r="H116" s="37" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I116" s="49" t="s">
         <v>493</v>
       </c>
       <c r="J116" s="21" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="K116" s="48" t="s">
         <v>494</v>
@@ -57675,37 +57673,37 @@
         <v>485</v>
       </c>
       <c r="AD116" s="24" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="AE116" s="53" t="s">
         <v>487</v>
       </c>
       <c r="AF116" s="24" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="AG116" s="53" t="s">
         <v>489</v>
       </c>
       <c r="AH116" s="67" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="AI116" s="69" t="s">
         <v>491</v>
       </c>
       <c r="AJ116" s="67" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="AK116" s="69" t="s">
         <v>493</v>
       </c>
       <c r="AL116" s="24" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="AM116" s="53" t="s">
         <v>494</v>
       </c>
       <c r="AN116" s="24" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="AO116" s="53" t="s">
         <v>495</v>
@@ -57721,13 +57719,13 @@
         <v>485</v>
       </c>
       <c r="BF116" s="41" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="BG116" s="56" t="s">
         <v>487</v>
       </c>
       <c r="BH116" s="41" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="BI116" s="56" t="s">
         <v>489</v>
@@ -57736,13 +57734,13 @@
         <v>485</v>
       </c>
       <c r="BR116" s="76" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="BS116" s="78" t="s">
         <v>491</v>
       </c>
       <c r="BT116" s="76" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="BU116" s="78" t="s">
         <v>493</v>
@@ -57759,25 +57757,25 @@
         <v>694</v>
       </c>
       <c r="CT116" s="46" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="CU116" s="19" t="s">
         <v>696</v>
       </c>
       <c r="CV116" s="46" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="CW116" s="19" t="s">
         <v>698</v>
       </c>
       <c r="CX116" s="46" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="CY116" s="19" t="s">
         <v>700</v>
       </c>
       <c r="CZ116" s="46" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="DA116" s="19" t="s">
         <v>702</v>
@@ -57788,7 +57786,7 @@
         <v>522</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="C117" s="48" t="s">
         <v>524</v>
@@ -57800,25 +57798,25 @@
         <v>526</v>
       </c>
       <c r="F117" s="37" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="G117" s="49" t="s">
         <v>527</v>
       </c>
       <c r="H117" s="37" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="I117" s="49" t="s">
         <v>529</v>
       </c>
       <c r="J117" s="21" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="K117" s="48" t="s">
         <v>530</v>
       </c>
       <c r="L117" s="21" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="M117" s="48" t="s">
         <v>531</v>
@@ -57833,37 +57831,37 @@
         <v>522</v>
       </c>
       <c r="AD117" s="24" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="AE117" s="53" t="s">
         <v>524</v>
       </c>
       <c r="AF117" s="24" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="AG117" s="53" t="s">
         <v>526</v>
       </c>
       <c r="AH117" s="67" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="AI117" s="69" t="s">
         <v>527</v>
       </c>
       <c r="AJ117" s="67" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="AK117" s="69" t="s">
         <v>529</v>
       </c>
       <c r="AL117" s="24" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="AM117" s="53" t="s">
         <v>530</v>
       </c>
       <c r="AN117" s="24" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="AO117" s="53" t="s">
         <v>531</v>
@@ -57879,13 +57877,13 @@
         <v>522</v>
       </c>
       <c r="BF117" s="41" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="BG117" s="56" t="s">
         <v>524</v>
       </c>
       <c r="BH117" s="41" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="BI117" s="56" t="s">
         <v>526</v>
@@ -57894,13 +57892,13 @@
         <v>522</v>
       </c>
       <c r="BR117" s="76" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="BS117" s="78" t="s">
         <v>527</v>
       </c>
       <c r="BT117" s="76" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="BU117" s="78" t="s">
         <v>529</v>
@@ -57931,25 +57929,25 @@
         <v>727</v>
       </c>
       <c r="CT117" s="46" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="CU117" s="19" t="s">
         <v>729</v>
       </c>
       <c r="CV117" s="46" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="CW117" s="19" t="s">
         <v>731</v>
       </c>
       <c r="CX117" s="46" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="CY117" s="19" t="s">
         <v>733</v>
       </c>
       <c r="CZ117" s="46" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="DA117" s="19" t="s">
         <v>735</v>
@@ -57972,19 +57970,19 @@
         <v>555</v>
       </c>
       <c r="F118" s="37" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="G118" s="49" t="s">
         <v>556</v>
       </c>
       <c r="H118" s="37" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I118" s="49" t="s">
         <v>557</v>
       </c>
       <c r="J118" s="21" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="K118" s="48" t="s">
         <v>559</v>
@@ -58005,37 +58003,37 @@
         <v>552</v>
       </c>
       <c r="AD118" s="24" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="AE118" s="53" t="s">
         <v>554</v>
       </c>
       <c r="AF118" s="24" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="AG118" s="53" t="s">
         <v>555</v>
       </c>
       <c r="AH118" s="67" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="AI118" s="69" t="s">
         <v>556</v>
       </c>
       <c r="AJ118" s="67" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="AK118" s="69" t="s">
         <v>557</v>
       </c>
       <c r="AL118" s="24" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="AM118" s="53" t="s">
         <v>559</v>
       </c>
       <c r="AN118" s="24" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="AO118" s="53" t="s">
         <v>560</v>
@@ -58051,13 +58049,13 @@
         <v>552</v>
       </c>
       <c r="BF118" s="41" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="BG118" s="56" t="s">
         <v>554</v>
       </c>
       <c r="BH118" s="41" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="BI118" s="56" t="s">
         <v>555</v>
@@ -58066,13 +58064,13 @@
         <v>552</v>
       </c>
       <c r="BR118" s="76" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="BS118" s="78" t="s">
         <v>556</v>
       </c>
       <c r="BT118" s="76" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="BU118" s="78" t="s">
         <v>557</v>
@@ -58081,31 +58079,31 @@
       <c r="CD118" s="22"/>
       <c r="CF118" s="22"/>
       <c r="CI118" s="79" t="s">
+        <v>1659</v>
+      </c>
+      <c r="CJ118" s="59" t="s">
+        <v>1660</v>
+      </c>
+      <c r="CK118" s="60" t="s">
         <v>1661</v>
       </c>
-      <c r="CJ118" s="59" t="s">
+      <c r="CL118" s="59" t="s">
         <v>1662</v>
       </c>
-      <c r="CK118" s="60" t="s">
+      <c r="CM118" s="60" t="s">
         <v>1663</v>
-      </c>
-      <c r="CL118" s="59" t="s">
-        <v>1664</v>
-      </c>
-      <c r="CM118" s="60" t="s">
-        <v>1665</v>
       </c>
       <c r="CN118" s="59" t="s">
         <v>697</v>
       </c>
       <c r="CO118" s="73" t="s">
+        <v>1664</v>
+      </c>
+      <c r="CP118" s="59" t="s">
+        <v>1665</v>
+      </c>
+      <c r="CQ118" s="73" t="s">
         <v>1666</v>
-      </c>
-      <c r="CP118" s="59" t="s">
-        <v>1667</v>
-      </c>
-      <c r="CQ118" s="73" t="s">
-        <v>1668</v>
       </c>
       <c r="CS118" s="2"/>
       <c r="CT118" s="2"/>
@@ -58134,25 +58132,25 @@
         <v>582</v>
       </c>
       <c r="F119" s="37" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="G119" s="49" t="s">
         <v>583</v>
       </c>
       <c r="H119" s="37" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="I119" s="49" t="s">
         <v>584</v>
       </c>
       <c r="J119" s="21" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="K119" s="48" t="s">
         <v>585</v>
       </c>
       <c r="L119" s="21" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="M119" s="48" t="s">
         <v>586</v>
@@ -58167,37 +58165,37 @@
         <v>579</v>
       </c>
       <c r="AD119" s="24" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="AE119" s="53" t="s">
         <v>581</v>
       </c>
       <c r="AF119" s="24" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="AG119" s="53" t="s">
         <v>582</v>
       </c>
       <c r="AH119" s="67" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="AI119" s="69" t="s">
         <v>583</v>
       </c>
       <c r="AJ119" s="67" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="AK119" s="69" t="s">
         <v>584</v>
       </c>
       <c r="AL119" s="24" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="AM119" s="53" t="s">
         <v>585</v>
       </c>
       <c r="AN119" s="24" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="AO119" s="53" t="s">
         <v>586</v>
@@ -58213,13 +58211,13 @@
         <v>579</v>
       </c>
       <c r="BF119" s="41" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="BG119" s="56" t="s">
         <v>581</v>
       </c>
       <c r="BH119" s="41" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="BI119" s="56" t="s">
         <v>582</v>
@@ -58228,13 +58226,13 @@
         <v>579</v>
       </c>
       <c r="BR119" s="76" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="BS119" s="78" t="s">
         <v>583</v>
       </c>
       <c r="BT119" s="76" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="BU119" s="78" t="s">
         <v>584</v>
@@ -58243,31 +58241,31 @@
       <c r="CD119" s="22"/>
       <c r="CF119" s="22"/>
       <c r="CI119" s="79" t="s">
+        <v>1667</v>
+      </c>
+      <c r="CJ119" s="59" t="s">
+        <v>1668</v>
+      </c>
+      <c r="CK119" s="60" t="s">
         <v>1669</v>
-      </c>
-      <c r="CJ119" s="59" t="s">
-        <v>1670</v>
-      </c>
-      <c r="CK119" s="60" t="s">
-        <v>1671</v>
       </c>
       <c r="CL119" s="59" t="s">
         <v>697</v>
       </c>
       <c r="CM119" s="60" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="CN119" s="59" t="s">
         <v>699</v>
       </c>
       <c r="CO119" s="73" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="CP119" s="59" t="s">
         <v>701</v>
       </c>
       <c r="CQ119" s="73" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="56.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -58287,13 +58285,13 @@
         <v>603</v>
       </c>
       <c r="F120" s="37" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="G120" s="49" t="s">
         <v>605</v>
       </c>
       <c r="H120" s="37" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="I120" s="49" t="s">
         <v>607</v>
@@ -58320,37 +58318,37 @@
         <v>599</v>
       </c>
       <c r="AD120" s="24" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="AE120" s="53" t="s">
         <v>601</v>
       </c>
       <c r="AF120" s="24" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="AG120" s="53" t="s">
         <v>603</v>
       </c>
       <c r="AH120" s="67" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="AI120" s="69" t="s">
         <v>605</v>
       </c>
       <c r="AJ120" s="67" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="AK120" s="69" t="s">
         <v>607</v>
       </c>
       <c r="AL120" s="24" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="AM120" s="53" t="s">
         <v>608</v>
       </c>
       <c r="AN120" s="24" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="AO120" s="53" t="s">
         <v>609</v>
@@ -58366,13 +58364,13 @@
         <v>599</v>
       </c>
       <c r="BF120" s="41" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="BG120" s="56" t="s">
         <v>601</v>
       </c>
       <c r="BH120" s="41" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="BI120" s="56" t="s">
         <v>603</v>
@@ -58381,13 +58379,13 @@
         <v>599</v>
       </c>
       <c r="BR120" s="76" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="BS120" s="78" t="s">
         <v>605</v>
       </c>
       <c r="BT120" s="76" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="BU120" s="78" t="s">
         <v>607</v>
@@ -58396,31 +58394,31 @@
       <c r="CD120" s="22"/>
       <c r="CF120" s="22"/>
       <c r="CI120" s="59" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="CJ120" s="59" t="s">
         <v>732</v>
       </c>
       <c r="CK120" s="60" t="s">
+        <v>1684</v>
+      </c>
+      <c r="CL120" s="59" t="s">
+        <v>1685</v>
+      </c>
+      <c r="CM120" s="60" t="s">
         <v>1686</v>
       </c>
-      <c r="CL120" s="59" t="s">
+      <c r="CN120" s="59" t="s">
         <v>1687</v>
       </c>
-      <c r="CM120" s="60" t="s">
+      <c r="CO120" s="73" t="s">
         <v>1688</v>
       </c>
-      <c r="CN120" s="59" t="s">
+      <c r="CP120" s="59" t="s">
         <v>1689</v>
       </c>
-      <c r="CO120" s="73" t="s">
+      <c r="CQ120" s="73" t="s">
         <v>1690</v>
-      </c>
-      <c r="CP120" s="59" t="s">
-        <v>1691</v>
-      </c>
-      <c r="CQ120" s="73" t="s">
-        <v>1692</v>
       </c>
       <c r="CS120" s="46" t="s">
         <v>381</v>
@@ -58453,19 +58451,19 @@
         <v>632</v>
       </c>
       <c r="D121" s="21" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="E121" s="48" t="s">
         <v>633</v>
       </c>
       <c r="F121" s="37" t="s">
-        <v>1603</v>
+        <v>983</v>
       </c>
       <c r="G121" s="49" t="s">
         <v>634</v>
       </c>
       <c r="H121" s="37" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="I121" s="49" t="s">
         <v>635</v>
@@ -58477,7 +58475,7 @@
         <v>636</v>
       </c>
       <c r="L121" s="21" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="M121" s="48" t="s">
         <v>638</v>
@@ -58492,7 +58490,7 @@
         <v>639</v>
       </c>
       <c r="AD121" s="24" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="AE121" s="53" t="s">
         <v>639</v>
@@ -58518,13 +58516,13 @@
         <v>630</v>
       </c>
       <c r="BF121" s="41" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="BG121" s="56" t="s">
         <v>632</v>
       </c>
       <c r="BH121" s="41" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="BI121" s="56" t="s">
         <v>633</v>
@@ -58533,13 +58531,13 @@
         <v>630</v>
       </c>
       <c r="BR121" s="76" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="BS121" s="78" t="s">
         <v>634</v>
       </c>
       <c r="BT121" s="76" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="BU121" s="78" t="s">
         <v>635</v>
@@ -58560,25 +58558,25 @@
         <v>446</v>
       </c>
       <c r="CT121" s="70" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="CU121" s="71" t="s">
         <v>448</v>
       </c>
       <c r="CV121" s="70" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="CW121" s="71" t="s">
         <v>450</v>
       </c>
       <c r="CX121" s="70" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="CY121" s="71" t="s">
         <v>452</v>
       </c>
       <c r="CZ121" s="70" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="DA121" s="71" t="s">
         <v>454</v>
@@ -58628,7 +58626,7 @@
         <v>639</v>
       </c>
       <c r="BF122" s="41" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="BG122" s="56" t="s">
         <v>639</v>
@@ -58639,7 +58637,7 @@
         <v>639</v>
       </c>
       <c r="BR122" s="76" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="BS122" s="57" t="s">
         <v>639</v>
@@ -58653,25 +58651,25 @@
         <v>473</v>
       </c>
       <c r="CT122" s="70" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="CU122" s="71" t="s">
         <v>475</v>
       </c>
       <c r="CV122" s="70" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="CW122" s="71" t="s">
         <v>477</v>
       </c>
       <c r="CX122" s="70" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="CY122" s="71" t="s">
         <v>479</v>
       </c>
       <c r="CZ122" s="70" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="DA122" s="71" t="s">
         <v>481</v>
@@ -58756,25 +58754,25 @@
         <v>510</v>
       </c>
       <c r="CT123" s="70" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="CU123" s="71" t="s">
         <v>512</v>
       </c>
       <c r="CV123" s="70" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="CW123" s="71" t="s">
         <v>514</v>
       </c>
       <c r="CX123" s="70" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="CY123" s="71" t="s">
         <v>515</v>
       </c>
       <c r="CZ123" s="70" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="DA123" s="71" t="s">
         <v>517</v>
@@ -58797,7 +58795,7 @@
         <v>420</v>
       </c>
       <c r="AD124" s="24" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="AE124" s="53" t="s">
         <v>422</v>
@@ -58809,25 +58807,25 @@
         <v>424</v>
       </c>
       <c r="AH124" s="67" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="AI124" s="69" t="s">
         <v>426</v>
       </c>
       <c r="AJ124" s="67" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="AK124" s="69" t="s">
         <v>428</v>
       </c>
       <c r="AL124" s="24" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="AM124" s="53" t="s">
         <v>430</v>
       </c>
       <c r="AN124" s="24" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="AO124" s="53" t="s">
         <v>432</v>
@@ -58883,37 +58881,37 @@
         <v>1259</v>
       </c>
       <c r="CO124" s="60" t="s">
+        <v>1714</v>
+      </c>
+      <c r="CP124" s="59" t="s">
+        <v>1715</v>
+      </c>
+      <c r="CQ124" s="60" t="s">
         <v>1716</v>
-      </c>
-      <c r="CP124" s="59" t="s">
-        <v>1717</v>
-      </c>
-      <c r="CQ124" s="60" t="s">
-        <v>1718</v>
       </c>
       <c r="CS124" s="46" t="s">
         <v>541</v>
       </c>
       <c r="CT124" s="46" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="CU124" s="19" t="s">
         <v>543</v>
       </c>
       <c r="CV124" s="46" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="CW124" s="19" t="s">
         <v>545</v>
       </c>
       <c r="CX124" s="46" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="CY124" s="19" t="s">
         <v>547</v>
       </c>
       <c r="CZ124" s="46" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="DA124" s="19" t="s">
         <v>549</v>
@@ -58957,7 +58955,7 @@
         <v>458</v>
       </c>
       <c r="AD125" s="24" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="AE125" s="53" t="s">
         <v>459</v>
@@ -58969,25 +58967,25 @@
         <v>461</v>
       </c>
       <c r="AH125" s="67" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="AI125" s="69" t="s">
         <v>462</v>
       </c>
       <c r="AJ125" s="67" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="AK125" s="69" t="s">
         <v>463</v>
       </c>
       <c r="AL125" s="24" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="AM125" s="53" t="s">
         <v>464</v>
       </c>
       <c r="AN125" s="24" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="AO125" s="53" t="s">
         <v>466</v>
@@ -59018,13 +59016,13 @@
         <v>420</v>
       </c>
       <c r="BR125" s="76" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="BS125" s="78" t="s">
         <v>426</v>
       </c>
       <c r="BT125" s="76" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="BU125" s="78" t="s">
         <v>428</v>
@@ -59039,49 +59037,49 @@
         <v>460</v>
       </c>
       <c r="CK125" s="60" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="CL125" s="59" t="s">
         <v>1259</v>
       </c>
       <c r="CM125" s="60" t="s">
+        <v>1725</v>
+      </c>
+      <c r="CN125" s="59" t="s">
+        <v>1726</v>
+      </c>
+      <c r="CO125" s="60" t="s">
         <v>1727</v>
       </c>
-      <c r="CN125" s="59" t="s">
+      <c r="CP125" s="59" t="s">
         <v>1728</v>
       </c>
-      <c r="CO125" s="60" t="s">
+      <c r="CQ125" s="60" t="s">
         <v>1729</v>
-      </c>
-      <c r="CP125" s="59" t="s">
-        <v>1730</v>
-      </c>
-      <c r="CQ125" s="60" t="s">
-        <v>1731</v>
       </c>
       <c r="CS125" s="46" t="s">
         <v>570</v>
       </c>
       <c r="CT125" s="46" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="CU125" s="19" t="s">
         <v>572</v>
       </c>
       <c r="CV125" s="46" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="CW125" s="19" t="s">
         <v>573</v>
       </c>
       <c r="CX125" s="46" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="CY125" s="19" t="s">
         <v>575</v>
       </c>
       <c r="CZ125" s="46" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="DA125" s="19" t="s">
         <v>577</v>
@@ -59110,7 +59108,7 @@
         <v>426</v>
       </c>
       <c r="H126" s="37" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="I126" s="49" t="s">
         <v>428</v>
@@ -59137,37 +59135,37 @@
         <v>485</v>
       </c>
       <c r="AD126" s="24" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="AE126" s="53" t="s">
         <v>487</v>
       </c>
       <c r="AF126" s="24" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="AG126" s="53" t="s">
         <v>489</v>
       </c>
       <c r="AH126" s="67" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="AI126" s="69" t="s">
         <v>491</v>
       </c>
       <c r="AJ126" s="67" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="AK126" s="69" t="s">
         <v>493</v>
       </c>
       <c r="AL126" s="24" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="AM126" s="53" t="s">
         <v>494</v>
       </c>
       <c r="AN126" s="24" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="AO126" s="53" t="s">
         <v>495</v>
@@ -59198,13 +59196,13 @@
         <v>458</v>
       </c>
       <c r="BR126" s="76" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="BS126" s="78" t="s">
         <v>462</v>
       </c>
       <c r="BT126" s="76" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="BU126" s="78" t="s">
         <v>463</v>
@@ -59219,49 +59217,49 @@
         <v>429</v>
       </c>
       <c r="CK126" s="60" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="CL126" s="59" t="s">
         <v>1271</v>
       </c>
       <c r="CM126" s="60" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="CN126" s="59" t="s">
         <v>194</v>
       </c>
       <c r="CO126" s="60" t="s">
+        <v>1741</v>
+      </c>
+      <c r="CP126" s="59" t="s">
+        <v>1742</v>
+      </c>
+      <c r="CQ126" s="60" t="s">
         <v>1743</v>
-      </c>
-      <c r="CP126" s="59" t="s">
-        <v>1744</v>
-      </c>
-      <c r="CQ126" s="60" t="s">
-        <v>1745</v>
       </c>
       <c r="CS126" s="46" t="s">
         <v>592</v>
       </c>
       <c r="CT126" s="46" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="CU126" s="19" t="s">
         <v>593</v>
       </c>
       <c r="CV126" s="46" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="CW126" s="19" t="s">
         <v>594</v>
       </c>
       <c r="CX126" s="46" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="CY126" s="19" t="s">
         <v>595</v>
       </c>
       <c r="CZ126" s="46" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="DA126" s="19" t="s">
         <v>597</v>
@@ -59272,7 +59270,7 @@
         <v>458</v>
       </c>
       <c r="B127" s="21" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="C127" s="48" t="s">
         <v>459</v>
@@ -59284,13 +59282,13 @@
         <v>461</v>
       </c>
       <c r="F127" s="37" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="G127" s="49" t="s">
         <v>462</v>
       </c>
       <c r="H127" s="37" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="I127" s="49" t="s">
         <v>463</v>
@@ -59302,7 +59300,7 @@
         <v>464</v>
       </c>
       <c r="L127" s="21" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="M127" s="48" t="s">
         <v>466</v>
@@ -59317,37 +59315,37 @@
         <v>522</v>
       </c>
       <c r="AD127" s="24" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="AE127" s="53" t="s">
         <v>524</v>
       </c>
       <c r="AF127" s="24" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="AG127" s="53" t="s">
         <v>526</v>
       </c>
       <c r="AH127" s="67" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="AI127" s="69" t="s">
         <v>527</v>
       </c>
       <c r="AJ127" s="67" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="AK127" s="69" t="s">
         <v>529</v>
       </c>
       <c r="AL127" s="24" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="AM127" s="53" t="s">
         <v>530</v>
       </c>
       <c r="AN127" s="24" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="AO127" s="53" t="s">
         <v>531</v>
@@ -59363,7 +59361,7 @@
         <v>485</v>
       </c>
       <c r="BF127" s="41" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="BG127" s="56" t="s">
         <v>487</v>
@@ -59378,13 +59376,13 @@
         <v>485</v>
       </c>
       <c r="BR127" s="76" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="BS127" s="78" t="s">
         <v>491</v>
       </c>
       <c r="BT127" s="76" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="BU127" s="78" t="s">
         <v>493</v>
@@ -59405,19 +59403,19 @@
         <v>621</v>
       </c>
       <c r="CT127" s="70" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="CU127" s="71" t="s">
         <v>623</v>
       </c>
       <c r="CV127" s="70" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="CW127" s="71" t="s">
         <v>625</v>
       </c>
       <c r="CX127" s="70" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="CY127" s="71" t="s">
         <v>627</v>
@@ -59438,19 +59436,19 @@
         <v>487</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="E128" s="48" t="s">
         <v>489</v>
       </c>
       <c r="F128" s="37" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="G128" s="49" t="s">
         <v>491</v>
       </c>
       <c r="H128" s="37" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="I128" s="49" t="s">
         <v>493</v>
@@ -59462,7 +59460,7 @@
         <v>494</v>
       </c>
       <c r="L128" s="21" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="M128" s="48" t="s">
         <v>495</v>
@@ -59477,37 +59475,37 @@
         <v>552</v>
       </c>
       <c r="AD128" s="24" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="AE128" s="53" t="s">
         <v>554</v>
       </c>
       <c r="AF128" s="24" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="AG128" s="53" t="s">
         <v>555</v>
       </c>
       <c r="AH128" s="67" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="AI128" s="69" t="s">
         <v>556</v>
       </c>
       <c r="AJ128" s="67" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="AK128" s="69" t="s">
         <v>557</v>
       </c>
       <c r="AL128" s="24" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="AM128" s="53" t="s">
         <v>559</v>
       </c>
       <c r="AN128" s="24" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="AO128" s="53" t="s">
         <v>560</v>
@@ -59529,7 +59527,7 @@
         <v>524</v>
       </c>
       <c r="BH128" s="41" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="BI128" s="56" t="s">
         <v>526</v>
@@ -59538,13 +59536,13 @@
         <v>522</v>
       </c>
       <c r="BR128" s="76" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="BS128" s="78" t="s">
         <v>527</v>
       </c>
       <c r="BT128" s="76" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="BU128" s="78" t="s">
         <v>529</v>
@@ -59556,13 +59554,13 @@
         <v>645</v>
       </c>
       <c r="CT128" s="70" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="CU128" s="71" t="s">
         <v>647</v>
       </c>
       <c r="CV128" s="70" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="CW128" s="71" t="s">
         <v>649</v>
@@ -59587,31 +59585,31 @@
         <v>524</v>
       </c>
       <c r="D129" s="21" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="E129" s="48" t="s">
         <v>526</v>
       </c>
       <c r="F129" s="37" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="G129" s="49" t="s">
         <v>527</v>
       </c>
       <c r="H129" s="37" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="I129" s="49" t="s">
         <v>529</v>
       </c>
       <c r="J129" s="21" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="K129" s="48" t="s">
         <v>530</v>
       </c>
       <c r="L129" s="21" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="M129" s="48" t="s">
         <v>531</v>
@@ -59626,37 +59624,37 @@
         <v>579</v>
       </c>
       <c r="AD129" s="24" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="AE129" s="53" t="s">
         <v>581</v>
       </c>
       <c r="AF129" s="24" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="AG129" s="53" t="s">
         <v>582</v>
       </c>
       <c r="AH129" s="67" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="AI129" s="69" t="s">
         <v>583</v>
       </c>
       <c r="AJ129" s="67" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="AK129" s="69" t="s">
         <v>584</v>
       </c>
       <c r="AL129" s="24" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="AM129" s="53" t="s">
         <v>585</v>
       </c>
       <c r="AN129" s="24" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="AO129" s="53" t="s">
         <v>586</v>
@@ -59672,7 +59670,7 @@
         <v>552</v>
       </c>
       <c r="BF129" s="41" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="BG129" s="56" t="s">
         <v>554</v>
@@ -59687,13 +59685,13 @@
         <v>552</v>
       </c>
       <c r="BR129" s="76" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="BS129" s="78" t="s">
         <v>556</v>
       </c>
       <c r="BT129" s="76" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="BU129" s="78" t="s">
         <v>557</v>
@@ -59724,25 +59722,25 @@
         <v>655</v>
       </c>
       <c r="CT129" s="70" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="CU129" s="71" t="s">
         <v>657</v>
       </c>
       <c r="CV129" s="70" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="CW129" s="71" t="s">
         <v>659</v>
       </c>
       <c r="CX129" s="70" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="CY129" s="71" t="s">
         <v>661</v>
       </c>
       <c r="CZ129" s="70" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="DA129" s="71" t="s">
         <v>663</v>
@@ -59753,37 +59751,37 @@
         <v>552</v>
       </c>
       <c r="B130" s="21" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="C130" s="48" t="s">
         <v>554</v>
       </c>
       <c r="D130" s="21" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="E130" s="48" t="s">
         <v>555</v>
       </c>
       <c r="F130" s="37" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="G130" s="49" t="s">
         <v>556</v>
       </c>
       <c r="H130" s="37" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="I130" s="49" t="s">
         <v>557</v>
       </c>
       <c r="J130" s="21" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="K130" s="48" t="s">
         <v>559</v>
       </c>
       <c r="L130" s="21" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="M130" s="48" t="s">
         <v>560</v>
@@ -59798,37 +59796,37 @@
         <v>599</v>
       </c>
       <c r="AD130" s="24" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="AE130" s="53" t="s">
         <v>601</v>
       </c>
       <c r="AF130" s="24" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="AG130" s="53" t="s">
         <v>603</v>
       </c>
       <c r="AH130" s="67" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="AI130" s="69" t="s">
         <v>605</v>
       </c>
       <c r="AJ130" s="67" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="AK130" s="69" t="s">
         <v>607</v>
       </c>
       <c r="AL130" s="24" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="AM130" s="53" t="s">
         <v>608</v>
       </c>
       <c r="AN130" s="24" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="AO130" s="53" t="s">
         <v>609</v>
@@ -59850,7 +59848,7 @@
         <v>581</v>
       </c>
       <c r="BH130" s="41" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="BI130" s="56" t="s">
         <v>582</v>
@@ -59859,13 +59857,13 @@
         <v>579</v>
       </c>
       <c r="BR130" s="76" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="BS130" s="78" t="s">
         <v>583</v>
       </c>
       <c r="BT130" s="76" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="BU130" s="78" t="s">
         <v>584</v>
@@ -59904,25 +59902,25 @@
         <v>667</v>
       </c>
       <c r="CT130" s="46" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="CU130" s="19" t="s">
         <v>669</v>
       </c>
       <c r="CV130" s="46" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="CW130" s="19" t="s">
         <v>671</v>
       </c>
       <c r="CX130" s="46" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="CY130" s="19" t="s">
         <v>673</v>
       </c>
       <c r="CZ130" s="46" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="DA130" s="19" t="s">
         <v>675</v>
@@ -59939,31 +59937,31 @@
         <v>581</v>
       </c>
       <c r="D131" s="21" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="E131" s="48" t="s">
         <v>582</v>
       </c>
       <c r="F131" s="37" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="G131" s="49" t="s">
         <v>583</v>
       </c>
       <c r="H131" s="37" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="I131" s="49" t="s">
         <v>584</v>
       </c>
       <c r="J131" s="21" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="K131" s="48" t="s">
         <v>585</v>
       </c>
       <c r="L131" s="21" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="M131" s="48" t="s">
         <v>586</v>
@@ -59978,7 +59976,7 @@
         <v>639</v>
       </c>
       <c r="AD131" s="24" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="AE131" s="53" t="s">
         <v>639</v>
@@ -60010,7 +60008,7 @@
         <v>601</v>
       </c>
       <c r="BH131" s="41" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="BI131" s="56" t="s">
         <v>603</v>
@@ -60019,13 +60017,13 @@
         <v>599</v>
       </c>
       <c r="BR131" s="76" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="BS131" s="78" t="s">
         <v>605</v>
       </c>
       <c r="BT131" s="76" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="BU131" s="78" t="s">
         <v>607</v>
@@ -60064,25 +60062,25 @@
         <v>694</v>
       </c>
       <c r="CT131" s="46" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="CU131" s="19" t="s">
         <v>696</v>
       </c>
       <c r="CV131" s="46" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="CW131" s="19" t="s">
         <v>698</v>
       </c>
       <c r="CX131" s="46" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="CY131" s="19" t="s">
         <v>700</v>
       </c>
       <c r="CZ131" s="46" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="DA131" s="19" t="s">
         <v>702</v>
@@ -60099,31 +60097,31 @@
         <v>601</v>
       </c>
       <c r="D132" s="21" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="E132" s="48" t="s">
         <v>603</v>
       </c>
       <c r="F132" s="37" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="G132" s="49" t="s">
         <v>605</v>
       </c>
       <c r="H132" s="37" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="I132" s="49" t="s">
         <v>607</v>
       </c>
       <c r="J132" s="21" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="K132" s="48" t="s">
         <v>608</v>
       </c>
       <c r="L132" s="21" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="M132" s="48" t="s">
         <v>609</v>
@@ -60167,13 +60165,13 @@
         <v>630</v>
       </c>
       <c r="BR132" s="76" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="BS132" s="78" t="s">
         <v>634</v>
       </c>
       <c r="BT132" s="76" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="BU132" s="78" t="s">
         <v>635</v>
@@ -60212,25 +60210,25 @@
         <v>727</v>
       </c>
       <c r="CT132" s="46" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="CU132" s="19" t="s">
         <v>729</v>
       </c>
       <c r="CV132" s="46" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="CW132" s="19" t="s">
         <v>731</v>
       </c>
       <c r="CX132" s="46" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="CY132" s="19" t="s">
         <v>733</v>
       </c>
       <c r="CZ132" s="46" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="DA132" s="19" t="s">
         <v>735</v>
@@ -60241,7 +60239,7 @@
         <v>630</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="C133" s="48" t="s">
         <v>632</v>
@@ -60253,25 +60251,25 @@
         <v>633</v>
       </c>
       <c r="F133" s="37" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="G133" s="49" t="s">
         <v>634</v>
       </c>
       <c r="H133" s="37" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="I133" s="49" t="s">
         <v>635</v>
       </c>
       <c r="J133" s="21" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="K133" s="48" t="s">
         <v>636</v>
       </c>
       <c r="L133" s="21" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="M133" s="48" t="s">
         <v>638</v>
@@ -60300,7 +60298,7 @@
         <v>639</v>
       </c>
       <c r="BF133" s="41" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="BG133" s="56" t="s">
         <v>639</v>
@@ -60311,7 +60309,7 @@
         <v>639</v>
       </c>
       <c r="BR133" s="76" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="BS133" s="57" t="s">
         <v>639</v>
@@ -60345,7 +60343,7 @@
         <v>639</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="C134" s="48" t="s">
         <v>639</v>
@@ -60525,13 +60523,13 @@
         <v>420</v>
       </c>
       <c r="BF136" s="41" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="BG136" s="56" t="s">
         <v>422</v>
       </c>
       <c r="BH136" s="41" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="BI136" s="56" t="s">
         <v>424</v>
@@ -60540,13 +60538,13 @@
         <v>420</v>
       </c>
       <c r="BR136" s="27" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="BS136" s="57" t="s">
         <v>426</v>
       </c>
       <c r="BT136" s="27" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="BU136" s="57" t="s">
         <v>428</v>
@@ -60564,7 +60562,7 @@
         <v>678</v>
       </c>
       <c r="CL136" s="59" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="CM136" s="60" t="s">
         <v>680</v>
@@ -60585,13 +60583,13 @@
         <v>676</v>
       </c>
       <c r="CT136" s="70" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="CU136" s="71" t="s">
         <v>678</v>
       </c>
       <c r="CV136" s="70" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="CW136" s="71" t="s">
         <v>680</v>
@@ -60661,13 +60659,13 @@
         <v>458</v>
       </c>
       <c r="BF137" s="41" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="BG137" s="56" t="s">
         <v>459</v>
       </c>
       <c r="BH137" s="41" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="BI137" s="56" t="s">
         <v>461</v>
@@ -60676,13 +60674,13 @@
         <v>458</v>
       </c>
       <c r="BR137" s="27" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="BS137" s="57" t="s">
         <v>462</v>
       </c>
       <c r="BT137" s="27" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="BU137" s="57" t="s">
         <v>463</v>
@@ -60706,7 +60704,7 @@
         <v>706</v>
       </c>
       <c r="CN137" s="59" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="CO137" s="60" t="s">
         <v>963</v>
@@ -60721,13 +60719,13 @@
         <v>703</v>
       </c>
       <c r="CT137" s="70" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="CU137" s="71" t="s">
         <v>704</v>
       </c>
       <c r="CV137" s="70" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="CW137" s="71" t="s">
         <v>706</v>
@@ -60797,13 +60795,13 @@
         <v>485</v>
       </c>
       <c r="BF138" s="41" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="BG138" s="56" t="s">
         <v>487</v>
       </c>
       <c r="BH138" s="41" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="BI138" s="56" t="s">
         <v>489</v>
@@ -60812,13 +60810,13 @@
         <v>485</v>
       </c>
       <c r="BR138" s="27" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="BS138" s="57" t="s">
         <v>491</v>
       </c>
       <c r="BT138" s="27" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="BU138" s="57" t="s">
         <v>493</v>
@@ -60842,13 +60840,13 @@
         <v>740</v>
       </c>
       <c r="CN138" s="59" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="CO138" s="60" t="s">
         <v>978</v>
       </c>
       <c r="CP138" s="59" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="CQ138" s="60" t="s">
         <v>980</v>
@@ -60857,13 +60855,13 @@
         <v>736</v>
       </c>
       <c r="CT138" s="70" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="CU138" s="71" t="s">
         <v>738</v>
       </c>
       <c r="CV138" s="70" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="CW138" s="71" t="s">
         <v>740</v>
@@ -60892,7 +60890,7 @@
         <v>491</v>
       </c>
       <c r="H139" s="37" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="I139" s="49" t="s">
         <v>493</v>
@@ -60933,13 +60931,13 @@
         <v>522</v>
       </c>
       <c r="BF139" s="41" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="BG139" s="56" t="s">
         <v>524</v>
       </c>
       <c r="BH139" s="41" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="BI139" s="56" t="s">
         <v>526</v>
@@ -60948,13 +60946,13 @@
         <v>522</v>
       </c>
       <c r="BR139" s="27" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="BS139" s="57" t="s">
         <v>527</v>
       </c>
       <c r="BT139" s="27" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="BU139" s="57" t="s">
         <v>529</v>
@@ -60982,7 +60980,7 @@
         <v>522</v>
       </c>
       <c r="B140" s="21" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="C140" s="48" t="s">
         <v>524</v>
@@ -61006,7 +61004,7 @@
         <v>529</v>
       </c>
       <c r="J140" s="21" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="K140" s="48" t="s">
         <v>530</v>
@@ -61041,13 +61039,13 @@
         <v>552</v>
       </c>
       <c r="BF140" s="41" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="BG140" s="56" t="s">
         <v>554</v>
       </c>
       <c r="BH140" s="41" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="BI140" s="56" t="s">
         <v>555</v>
@@ -61056,13 +61054,13 @@
         <v>552</v>
       </c>
       <c r="BR140" s="27" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="BS140" s="57" t="s">
         <v>556</v>
       </c>
       <c r="BT140" s="27" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="BU140" s="57" t="s">
         <v>557</v>
@@ -61094,7 +61092,7 @@
         <v>556</v>
       </c>
       <c r="H141" s="37" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="I141" s="49" t="s">
         <v>557</v>
@@ -61135,13 +61133,13 @@
         <v>579</v>
       </c>
       <c r="BF141" s="41" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="BG141" s="56" t="s">
         <v>581</v>
       </c>
       <c r="BH141" s="41" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="BI141" s="56" t="s">
         <v>582</v>
@@ -61150,13 +61148,13 @@
         <v>579</v>
       </c>
       <c r="BR141" s="27" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="BS141" s="57" t="s">
         <v>583</v>
       </c>
       <c r="BT141" s="27" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="BU141" s="57" t="s">
         <v>584</v>
@@ -61267,13 +61265,13 @@
         <v>599</v>
       </c>
       <c r="BF142" s="41" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="BG142" s="56" t="s">
         <v>601</v>
       </c>
       <c r="BH142" s="41" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="BI142" s="56" t="s">
         <v>603</v>
@@ -61282,13 +61280,13 @@
         <v>599</v>
       </c>
       <c r="BR142" s="27" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="BS142" s="57" t="s">
         <v>605</v>
       </c>
       <c r="BT142" s="27" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="BU142" s="57" t="s">
         <v>607</v>
@@ -61306,7 +61304,7 @@
         <v>678</v>
       </c>
       <c r="CL142" s="59" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="CM142" s="60" t="s">
         <v>680</v>
@@ -61327,25 +61325,25 @@
         <v>446</v>
       </c>
       <c r="CT142" s="70" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="CU142" s="71" t="s">
         <v>448</v>
       </c>
       <c r="CV142" s="70" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="CW142" s="71" t="s">
         <v>450</v>
       </c>
       <c r="CX142" s="70" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="CY142" s="71" t="s">
         <v>452</v>
       </c>
       <c r="CZ142" s="70" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="DA142" s="71" t="s">
         <v>454</v>
@@ -61374,7 +61372,7 @@
         <v>605</v>
       </c>
       <c r="H143" s="37" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="I143" s="49" t="s">
         <v>607</v>
@@ -61415,13 +61413,13 @@
         <v>630</v>
       </c>
       <c r="BF143" s="41" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="BG143" s="56" t="s">
         <v>632</v>
       </c>
       <c r="BH143" s="41" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="BI143" s="56" t="s">
         <v>633</v>
@@ -61430,13 +61428,13 @@
         <v>630</v>
       </c>
       <c r="BR143" s="27" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="BS143" s="57" t="s">
         <v>634</v>
       </c>
       <c r="BT143" s="27" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="BU143" s="57" t="s">
         <v>635</v>
@@ -61460,7 +61458,7 @@
         <v>706</v>
       </c>
       <c r="CN143" s="59" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="CO143" s="60" t="s">
         <v>963</v>
@@ -61475,25 +61473,25 @@
         <v>473</v>
       </c>
       <c r="CT143" s="70" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="CU143" s="71" t="s">
         <v>475</v>
       </c>
       <c r="CV143" s="70" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="CW143" s="71" t="s">
         <v>477</v>
       </c>
       <c r="CX143" s="70" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="CY143" s="71" t="s">
         <v>479</v>
       </c>
       <c r="CZ143" s="70" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="DA143" s="71" t="s">
         <v>481</v>
@@ -61563,7 +61561,7 @@
         <v>639</v>
       </c>
       <c r="BF144" s="41" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="BG144" s="56" t="s">
         <v>639</v>
@@ -61574,7 +61572,7 @@
         <v>639</v>
       </c>
       <c r="BR144" s="27" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="BS144" s="57" t="s">
         <v>639</v>
@@ -61600,13 +61598,13 @@
         <v>740</v>
       </c>
       <c r="CN144" s="59" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="CO144" s="60" t="s">
         <v>978</v>
       </c>
       <c r="CP144" s="59" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="CQ144" s="60" t="s">
         <v>980</v>
@@ -61615,25 +61613,25 @@
         <v>510</v>
       </c>
       <c r="CT144" s="70" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="CU144" s="71" t="s">
         <v>512</v>
       </c>
       <c r="CV144" s="70" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="CW144" s="71" t="s">
         <v>514</v>
       </c>
       <c r="CX144" s="70" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="CY144" s="71" t="s">
         <v>515</v>
       </c>
       <c r="CZ144" s="70" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="DA144" s="71" t="s">
         <v>517</v>
@@ -61701,25 +61699,25 @@
         <v>541</v>
       </c>
       <c r="CT145" s="46" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="CU145" s="19" t="s">
         <v>543</v>
       </c>
       <c r="CV145" s="46" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="CW145" s="19" t="s">
         <v>545</v>
       </c>
       <c r="CX145" s="46" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="CY145" s="19" t="s">
         <v>547</v>
       </c>
       <c r="CZ145" s="46" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="DA145" s="19" t="s">
         <v>549</v>
@@ -61800,25 +61798,25 @@
         <v>570</v>
       </c>
       <c r="CT146" s="46" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="CU146" s="19" t="s">
         <v>572</v>
       </c>
       <c r="CV146" s="46" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="CW146" s="19" t="s">
         <v>573</v>
       </c>
       <c r="CX146" s="46" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="CY146" s="19" t="s">
         <v>575</v>
       </c>
       <c r="CZ146" s="46" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="DA146" s="19" t="s">
         <v>577</v>
@@ -61906,55 +61904,55 @@
       <c r="CD147" s="22"/>
       <c r="CF147" s="22"/>
       <c r="CI147" s="79" t="s">
+        <v>1659</v>
+      </c>
+      <c r="CJ147" s="59" t="s">
+        <v>1872</v>
+      </c>
+      <c r="CK147" s="60" t="s">
         <v>1661</v>
       </c>
-      <c r="CJ147" s="59" t="s">
+      <c r="CL147" s="59" t="s">
+        <v>1873</v>
+      </c>
+      <c r="CM147" s="60" t="s">
+        <v>1663</v>
+      </c>
+      <c r="CN147" s="59" t="s">
         <v>1874</v>
       </c>
-      <c r="CK147" s="60" t="s">
-        <v>1663</v>
-      </c>
-      <c r="CL147" s="59" t="s">
+      <c r="CO147" s="73" t="s">
+        <v>1664</v>
+      </c>
+      <c r="CP147" s="59" t="s">
         <v>1875</v>
       </c>
-      <c r="CM147" s="60" t="s">
-        <v>1665</v>
-      </c>
-      <c r="CN147" s="59" t="s">
-        <v>1876</v>
-      </c>
-      <c r="CO147" s="73" t="s">
+      <c r="CQ147" s="73" t="s">
         <v>1666</v>
-      </c>
-      <c r="CP147" s="59" t="s">
-        <v>1877</v>
-      </c>
-      <c r="CQ147" s="73" t="s">
-        <v>1668</v>
       </c>
       <c r="CS147" s="46" t="s">
         <v>592</v>
       </c>
       <c r="CT147" s="46" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="CU147" s="19" t="s">
         <v>593</v>
       </c>
       <c r="CV147" s="46" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="CW147" s="19" t="s">
         <v>594</v>
       </c>
       <c r="CX147" s="46" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="CY147" s="19" t="s">
         <v>595</v>
       </c>
       <c r="CZ147" s="46" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="DA147" s="19" t="s">
         <v>597</v>
@@ -61971,7 +61969,7 @@
         <v>422</v>
       </c>
       <c r="D148" s="21" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="E148" s="48" t="s">
         <v>424</v>
@@ -61995,7 +61993,7 @@
         <v>430</v>
       </c>
       <c r="L148" s="21" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="M148" s="48" t="s">
         <v>432</v>
@@ -62039,7 +62037,7 @@
         <v>458</v>
       </c>
       <c r="BL148" s="41" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="BM148" s="56" t="s">
         <v>459</v>
@@ -62054,55 +62052,55 @@
       <c r="CD148" s="22"/>
       <c r="CF148" s="22"/>
       <c r="CI148" s="79" t="s">
+        <v>1667</v>
+      </c>
+      <c r="CJ148" s="59" t="s">
+        <v>1880</v>
+      </c>
+      <c r="CK148" s="60" t="s">
         <v>1669</v>
       </c>
-      <c r="CJ148" s="59" t="s">
-        <v>1882</v>
-      </c>
-      <c r="CK148" s="60" t="s">
-        <v>1671</v>
-      </c>
       <c r="CL148" s="59" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="CM148" s="60" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="CN148" s="59" t="s">
         <v>908</v>
       </c>
       <c r="CO148" s="73" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="CP148" s="59" t="s">
         <v>909</v>
       </c>
       <c r="CQ148" s="73" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="CS148" s="70" t="s">
         <v>621</v>
       </c>
       <c r="CT148" s="70" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="CU148" s="71" t="s">
         <v>623</v>
       </c>
       <c r="CV148" s="70" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="CW148" s="71" t="s">
         <v>625</v>
       </c>
       <c r="CX148" s="70" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="CY148" s="71" t="s">
         <v>627</v>
       </c>
       <c r="CZ148" s="70" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="DA148" s="71" t="s">
         <v>629</v>
@@ -62119,7 +62117,7 @@
         <v>459</v>
       </c>
       <c r="D149" s="21" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="E149" s="48" t="s">
         <v>461</v>
@@ -62143,7 +62141,7 @@
         <v>464</v>
       </c>
       <c r="L149" s="21" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="M149" s="48" t="s">
         <v>466</v>
@@ -62202,55 +62200,55 @@
       <c r="CD149" s="22"/>
       <c r="CF149" s="22"/>
       <c r="CI149" s="59" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="CJ149" s="59" t="s">
         <v>925</v>
       </c>
       <c r="CK149" s="60" t="s">
+        <v>1684</v>
+      </c>
+      <c r="CL149" s="59" t="s">
+        <v>1885</v>
+      </c>
+      <c r="CM149" s="60" t="s">
         <v>1686</v>
       </c>
-      <c r="CL149" s="59" t="s">
+      <c r="CN149" s="59" t="s">
+        <v>1886</v>
+      </c>
+      <c r="CO149" s="73" t="s">
+        <v>1688</v>
+      </c>
+      <c r="CP149" s="59" t="s">
         <v>1887</v>
       </c>
-      <c r="CM149" s="60" t="s">
-        <v>1688</v>
-      </c>
-      <c r="CN149" s="59" t="s">
-        <v>1888</v>
-      </c>
-      <c r="CO149" s="73" t="s">
+      <c r="CQ149" s="73" t="s">
         <v>1690</v>
-      </c>
-      <c r="CP149" s="59" t="s">
-        <v>1889</v>
-      </c>
-      <c r="CQ149" s="73" t="s">
-        <v>1692</v>
       </c>
       <c r="CS149" s="70" t="s">
         <v>645</v>
       </c>
       <c r="CT149" s="70" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="CU149" s="71" t="s">
         <v>647</v>
       </c>
       <c r="CV149" s="70" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="CW149" s="71" t="s">
         <v>649</v>
       </c>
       <c r="CX149" s="70" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="CY149" s="71" t="s">
         <v>651</v>
       </c>
       <c r="CZ149" s="70" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="DA149" s="71" t="s">
         <v>653</v>
@@ -62267,7 +62265,7 @@
         <v>487</v>
       </c>
       <c r="D150" s="21" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="E150" s="48" t="s">
         <v>489</v>
@@ -62279,7 +62277,7 @@
         <v>491</v>
       </c>
       <c r="H150" s="37" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="I150" s="49" t="s">
         <v>493</v>
@@ -62291,7 +62289,7 @@
         <v>494</v>
       </c>
       <c r="L150" s="21" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="M150" s="48" t="s">
         <v>495</v>
@@ -62320,7 +62318,7 @@
         <v>522</v>
       </c>
       <c r="BF150" s="41" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="BG150" s="56" t="s">
         <v>524</v>
@@ -62335,7 +62333,7 @@
         <v>522</v>
       </c>
       <c r="BL150" s="41" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="BM150" s="56" t="s">
         <v>524</v>
@@ -62353,25 +62351,25 @@
         <v>655</v>
       </c>
       <c r="CT150" s="70" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="CU150" s="71" t="s">
         <v>657</v>
       </c>
       <c r="CV150" s="70" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="CW150" s="71" t="s">
         <v>659</v>
       </c>
       <c r="CX150" s="70" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="CY150" s="71" t="s">
         <v>661</v>
       </c>
       <c r="CZ150" s="70" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="DA150" s="71" t="s">
         <v>663</v>
@@ -62388,7 +62386,7 @@
         <v>524</v>
       </c>
       <c r="D151" s="21" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="E151" s="48" t="s">
         <v>526</v>
@@ -62400,7 +62398,7 @@
         <v>527</v>
       </c>
       <c r="H151" s="37" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="I151" s="49" t="s">
         <v>529</v>
@@ -62412,7 +62410,7 @@
         <v>530</v>
       </c>
       <c r="L151" s="21" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="M151" s="48" t="s">
         <v>531</v>
@@ -62441,7 +62439,7 @@
         <v>552</v>
       </c>
       <c r="BF151" s="41" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="BG151" s="56" t="s">
         <v>554</v>
@@ -62456,7 +62454,7 @@
         <v>552</v>
       </c>
       <c r="BL151" s="41" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="BM151" s="56" t="s">
         <v>554</v>
@@ -62474,25 +62472,25 @@
         <v>667</v>
       </c>
       <c r="CT151" s="46" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="CU151" s="19" t="s">
         <v>669</v>
       </c>
       <c r="CV151" s="46" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="CW151" s="19" t="s">
         <v>671</v>
       </c>
       <c r="CX151" s="46" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="CY151" s="19" t="s">
         <v>673</v>
       </c>
       <c r="CZ151" s="46" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="DA151" s="19" t="s">
         <v>675</v>
@@ -62503,13 +62501,13 @@
         <v>552</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="C152" s="48" t="s">
         <v>554</v>
       </c>
       <c r="D152" s="21" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="E152" s="48" t="s">
         <v>555</v>
@@ -62521,19 +62519,19 @@
         <v>556</v>
       </c>
       <c r="H152" s="37" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="I152" s="49" t="s">
         <v>557</v>
       </c>
       <c r="J152" s="21" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="K152" s="48" t="s">
         <v>559</v>
       </c>
       <c r="L152" s="21" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="M152" s="48" t="s">
         <v>560</v>
@@ -62562,7 +62560,7 @@
         <v>579</v>
       </c>
       <c r="BF152" s="41" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="BG152" s="56" t="s">
         <v>581</v>
@@ -62577,7 +62575,7 @@
         <v>579</v>
       </c>
       <c r="BL152" s="41" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="BM152" s="56" t="s">
         <v>581</v>
@@ -62595,25 +62593,25 @@
         <v>694</v>
       </c>
       <c r="CT152" s="46" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="CU152" s="19" t="s">
         <v>696</v>
       </c>
       <c r="CV152" s="46" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="CW152" s="19" t="s">
         <v>698</v>
       </c>
       <c r="CX152" s="46" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="CY152" s="19" t="s">
         <v>700</v>
       </c>
       <c r="CZ152" s="46" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="DA152" s="19" t="s">
         <v>702</v>
@@ -62630,7 +62628,7 @@
         <v>581</v>
       </c>
       <c r="D153" s="21" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="E153" s="48" t="s">
         <v>582</v>
@@ -62642,7 +62640,7 @@
         <v>583</v>
       </c>
       <c r="H153" s="37" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="I153" s="49" t="s">
         <v>584</v>
@@ -62654,7 +62652,7 @@
         <v>585</v>
       </c>
       <c r="L153" s="21" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="M153" s="48" t="s">
         <v>586</v>
@@ -62698,7 +62696,7 @@
         <v>599</v>
       </c>
       <c r="BL153" s="41" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="BM153" s="56" t="s">
         <v>601</v>
@@ -62716,25 +62714,25 @@
         <v>727</v>
       </c>
       <c r="CT153" s="46" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="CU153" s="19" t="s">
         <v>729</v>
       </c>
       <c r="CV153" s="46" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="CW153" s="19" t="s">
         <v>731</v>
       </c>
       <c r="CX153" s="46" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="CY153" s="19" t="s">
         <v>733</v>
       </c>
       <c r="CZ153" s="46" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="DA153" s="19" t="s">
         <v>735</v>
@@ -62751,7 +62749,7 @@
         <v>601</v>
       </c>
       <c r="D154" s="21" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="E154" s="48" t="s">
         <v>603</v>
@@ -62763,7 +62761,7 @@
         <v>605</v>
       </c>
       <c r="H154" s="37" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="I154" s="49" t="s">
         <v>607</v>
@@ -62775,7 +62773,7 @@
         <v>608</v>
       </c>
       <c r="L154" s="21" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="M154" s="48" t="s">
         <v>609</v>
@@ -63075,13 +63073,13 @@
         <v>676</v>
       </c>
       <c r="CT158" s="70" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="CU158" s="71" t="s">
         <v>678</v>
       </c>
       <c r="CV158" s="70" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="CW158" s="71" t="s">
         <v>680</v>
@@ -63092,37 +63090,37 @@
         <v>420</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="C159" s="48" t="s">
         <v>422</v>
       </c>
       <c r="D159" s="21" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="E159" s="48" t="s">
         <v>424</v>
       </c>
       <c r="F159" s="37" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="G159" s="49" t="s">
         <v>426</v>
       </c>
       <c r="H159" s="37" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="I159" s="49" t="s">
         <v>428</v>
       </c>
       <c r="J159" s="21" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="K159" s="48" t="s">
         <v>430</v>
       </c>
       <c r="L159" s="21" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="M159" s="48" t="s">
         <v>432</v>
@@ -63151,13 +63149,13 @@
         <v>420</v>
       </c>
       <c r="BF159" s="41" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="BG159" s="56" t="s">
         <v>422</v>
       </c>
       <c r="BH159" s="41" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="BI159" s="56" t="s">
         <v>424</v>
@@ -63172,13 +63170,13 @@
         <v>703</v>
       </c>
       <c r="CT159" s="70" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="CU159" s="71" t="s">
         <v>704</v>
       </c>
       <c r="CV159" s="70" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="CW159" s="71" t="s">
         <v>706</v>
@@ -63189,37 +63187,37 @@
         <v>458</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="C160" s="48" t="s">
         <v>459</v>
       </c>
       <c r="D160" s="21" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="E160" s="48" t="s">
         <v>461</v>
       </c>
       <c r="F160" s="37" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="G160" s="49" t="s">
         <v>462</v>
       </c>
       <c r="H160" s="37" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="I160" s="49" t="s">
         <v>463</v>
       </c>
       <c r="J160" s="21" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="K160" s="48" t="s">
         <v>464</v>
       </c>
       <c r="L160" s="21" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="M160" s="48" t="s">
         <v>466</v>
@@ -63248,7 +63246,7 @@
         <v>458</v>
       </c>
       <c r="BF160" s="41" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="BG160" s="56" t="s">
         <v>459</v>
@@ -63269,13 +63267,13 @@
         <v>736</v>
       </c>
       <c r="CT160" s="70" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="CU160" s="71" t="s">
         <v>738</v>
       </c>
       <c r="CV160" s="70" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="CW160" s="71" t="s">
         <v>740</v>
@@ -63286,37 +63284,37 @@
         <v>485</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="C161" s="48" t="s">
         <v>487</v>
       </c>
       <c r="D161" s="21" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="E161" s="48" t="s">
         <v>489</v>
       </c>
       <c r="F161" s="37" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="G161" s="49" t="s">
         <v>491</v>
       </c>
       <c r="H161" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="I161" s="49" t="s">
         <v>493</v>
       </c>
       <c r="J161" s="21" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="K161" s="48" t="s">
         <v>494</v>
       </c>
       <c r="L161" s="21" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="M161" s="48" t="s">
         <v>495</v>
@@ -63351,7 +63349,7 @@
         <v>487</v>
       </c>
       <c r="BH161" s="41" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="BI161" s="56" t="s">
         <v>489</v>
@@ -63373,37 +63371,37 @@
         <v>522</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="C162" s="48" t="s">
         <v>524</v>
       </c>
       <c r="D162" s="21" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="E162" s="48" t="s">
         <v>526</v>
       </c>
       <c r="F162" s="37" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="G162" s="49" t="s">
         <v>527</v>
       </c>
       <c r="H162" s="37" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="I162" s="49" t="s">
         <v>529</v>
       </c>
       <c r="J162" s="21" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="K162" s="48" t="s">
         <v>530</v>
       </c>
       <c r="L162" s="21" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="M162" s="48" t="s">
         <v>531</v>
@@ -63438,7 +63436,7 @@
         <v>524</v>
       </c>
       <c r="BH162" s="41" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="BI162" s="56" t="s">
         <v>526</v>
@@ -63455,37 +63453,37 @@
         <v>552</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="C163" s="48" t="s">
         <v>554</v>
       </c>
       <c r="D163" s="21" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="E163" s="48" t="s">
         <v>555</v>
       </c>
       <c r="F163" s="37" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="G163" s="49" t="s">
         <v>556</v>
       </c>
       <c r="H163" s="37" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="I163" s="49" t="s">
         <v>557</v>
       </c>
       <c r="J163" s="21" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="K163" s="48" t="s">
         <v>559</v>
       </c>
       <c r="L163" s="21" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="M163" s="48" t="s">
         <v>560</v>
@@ -63514,13 +63512,13 @@
         <v>552</v>
       </c>
       <c r="BF163" s="41" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="BG163" s="56" t="s">
         <v>554</v>
       </c>
       <c r="BH163" s="41" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="BI163" s="56" t="s">
         <v>555</v>
@@ -63556,37 +63554,37 @@
         <v>579</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="C164" s="48" t="s">
         <v>581</v>
       </c>
       <c r="D164" s="21" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="E164" s="48" t="s">
         <v>582</v>
       </c>
       <c r="F164" s="37" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="G164" s="49" t="s">
         <v>583</v>
       </c>
       <c r="H164" s="37" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="I164" s="49" t="s">
         <v>584</v>
       </c>
       <c r="J164" s="21" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="K164" s="48" t="s">
         <v>585</v>
       </c>
       <c r="L164" s="21" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="M164" s="48" t="s">
         <v>586</v>
@@ -63621,7 +63619,7 @@
         <v>581</v>
       </c>
       <c r="BH164" s="41" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="BI164" s="56" t="s">
         <v>582</v>
@@ -63648,7 +63646,7 @@
         <v>450</v>
       </c>
       <c r="CX164" s="70" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="CY164" s="71" t="s">
         <v>452</v>
@@ -63665,37 +63663,37 @@
         <v>599</v>
       </c>
       <c r="B165" s="21" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="C165" s="48" t="s">
         <v>601</v>
       </c>
       <c r="D165" s="21" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="E165" s="48" t="s">
         <v>603</v>
       </c>
       <c r="F165" s="37" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="G165" s="49" t="s">
         <v>605</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="I165" s="49" t="s">
         <v>607</v>
       </c>
       <c r="J165" s="21" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="K165" s="48" t="s">
         <v>608</v>
       </c>
       <c r="L165" s="21" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="M165" s="48" t="s">
         <v>609</v>
@@ -63724,13 +63722,13 @@
         <v>599</v>
       </c>
       <c r="BF165" s="41" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="BG165" s="56" t="s">
         <v>601</v>
       </c>
       <c r="BH165" s="41" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="BI165" s="56" t="s">
         <v>603</v>
@@ -63766,7 +63764,7 @@
         <v>639</v>
       </c>
       <c r="B166" s="21" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="C166" s="48" t="s">
         <v>639</v>
@@ -63805,13 +63803,13 @@
         <v>630</v>
       </c>
       <c r="BF166" s="41" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="BG166" s="56" t="s">
         <v>632</v>
       </c>
       <c r="BH166" s="41" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="BI166" s="56" t="s">
         <v>633</v>
@@ -63880,7 +63878,7 @@
         <v>639</v>
       </c>
       <c r="BF167" s="41" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="BG167" s="56" t="s">
         <v>639</v>
@@ -63973,13 +63971,13 @@
         <v>573</v>
       </c>
       <c r="CX168" s="46" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="CY168" s="19" t="s">
         <v>575</v>
       </c>
       <c r="CZ168" s="46" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="DA168" s="19" t="s">
         <v>577</v>
@@ -64072,7 +64070,7 @@
         <v>595</v>
       </c>
       <c r="CZ169" s="46" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="DA169" s="19" t="s">
         <v>597</v>
@@ -64142,13 +64140,13 @@
         <v>420</v>
       </c>
       <c r="BF170" s="41" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="BG170" s="56" t="s">
         <v>422</v>
       </c>
       <c r="BH170" s="41" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="BI170" s="56" t="s">
         <v>424</v>
@@ -64163,7 +64161,7 @@
         <v>621</v>
       </c>
       <c r="CT170" s="70" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="CU170" s="71" t="s">
         <v>623</v>
@@ -64251,13 +64249,13 @@
         <v>458</v>
       </c>
       <c r="BF171" s="41" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="BG171" s="56" t="s">
         <v>459</v>
       </c>
       <c r="BH171" s="41" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="BI171" s="56" t="s">
         <v>461</v>
@@ -64272,13 +64270,13 @@
         <v>645</v>
       </c>
       <c r="CT171" s="70" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="CU171" s="71" t="s">
         <v>647</v>
       </c>
       <c r="CV171" s="70" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="CW171" s="71" t="s">
         <v>649</v>
@@ -64360,13 +64358,13 @@
         <v>485</v>
       </c>
       <c r="BF172" s="41" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="BG172" s="56" t="s">
         <v>487</v>
       </c>
       <c r="BH172" s="41" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="BI172" s="56" t="s">
         <v>489</v>
@@ -64381,13 +64379,13 @@
         <v>655</v>
       </c>
       <c r="CT172" s="70" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="CU172" s="71" t="s">
         <v>657</v>
       </c>
       <c r="CV172" s="70" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="CW172" s="71" t="s">
         <v>659</v>
@@ -64469,13 +64467,13 @@
         <v>522</v>
       </c>
       <c r="BF173" s="41" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="BG173" s="56" t="s">
         <v>524</v>
       </c>
       <c r="BH173" s="41" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="BI173" s="56" t="s">
         <v>526</v>
@@ -64490,25 +64488,25 @@
         <v>667</v>
       </c>
       <c r="CT173" s="46" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="CU173" s="19" t="s">
         <v>669</v>
       </c>
       <c r="CV173" s="46" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="CW173" s="19" t="s">
         <v>671</v>
       </c>
       <c r="CX173" s="46" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="CY173" s="19" t="s">
         <v>673</v>
       </c>
       <c r="CZ173" s="46" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="DA173" s="19" t="s">
         <v>675</v>
@@ -64578,13 +64576,13 @@
         <v>552</v>
       </c>
       <c r="BF174" s="41" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="BG174" s="56" t="s">
         <v>554</v>
       </c>
       <c r="BH174" s="41" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="BI174" s="56" t="s">
         <v>555</v>
@@ -64599,25 +64597,25 @@
         <v>694</v>
       </c>
       <c r="CT174" s="46" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="CU174" s="19" t="s">
         <v>696</v>
       </c>
       <c r="CV174" s="46" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="CW174" s="19" t="s">
         <v>698</v>
       </c>
       <c r="CX174" s="46" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="CY174" s="19" t="s">
         <v>700</v>
       </c>
       <c r="CZ174" s="46" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="DA174" s="19" t="s">
         <v>702</v>
@@ -64687,13 +64685,13 @@
         <v>579</v>
       </c>
       <c r="BF175" s="41" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="BG175" s="56" t="s">
         <v>581</v>
       </c>
       <c r="BH175" s="41" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="BI175" s="56" t="s">
         <v>582</v>
@@ -64708,25 +64706,25 @@
         <v>727</v>
       </c>
       <c r="CT175" s="46" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="CU175" s="19" t="s">
         <v>729</v>
       </c>
       <c r="CV175" s="46" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="CW175" s="19" t="s">
         <v>731</v>
       </c>
       <c r="CX175" s="46" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="CY175" s="19" t="s">
         <v>733</v>
       </c>
       <c r="CZ175" s="46" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="DA175" s="19" t="s">
         <v>735</v>
@@ -64796,13 +64794,13 @@
         <v>599</v>
       </c>
       <c r="BF176" s="41" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="BG176" s="56" t="s">
         <v>601</v>
       </c>
       <c r="BH176" s="41" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="BI176" s="56" t="s">
         <v>603</v>
@@ -64887,13 +64885,13 @@
         <v>630</v>
       </c>
       <c r="BF177" s="41" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="BG177" s="56" t="s">
         <v>632</v>
       </c>
       <c r="BH177" s="41" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="BI177" s="56" t="s">
         <v>633</v>
@@ -64949,7 +64947,7 @@
         <v>639</v>
       </c>
       <c r="BF178" s="41" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="BG178" s="56" t="s">
         <v>639</v>
@@ -65014,13 +65012,13 @@
         <v>676</v>
       </c>
       <c r="CT179" s="70" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="CU179" s="71" t="s">
         <v>678</v>
       </c>
       <c r="CV179" s="70" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="CW179" s="71" t="s">
         <v>680</v>
@@ -65099,7 +65097,7 @@
         <v>704</v>
       </c>
       <c r="CV180" s="70" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="CW180" s="71" t="s">
         <v>706</v>
@@ -65169,7 +65167,7 @@
         <v>420</v>
       </c>
       <c r="BF181" s="41" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="BG181" s="56" t="s">
         <v>422</v>
@@ -65190,7 +65188,7 @@
         <v>736</v>
       </c>
       <c r="CT181" s="70" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="CU181" s="71" t="s">
         <v>738</v>
@@ -65310,7 +65308,7 @@
         <v>491</v>
       </c>
       <c r="H183" s="37" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="I183" s="49" t="s">
         <v>493</v>
@@ -65351,7 +65349,7 @@
         <v>485</v>
       </c>
       <c r="BF183" s="41" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="BG183" s="56" t="s">
         <v>487</v>
@@ -65433,13 +65431,13 @@
         <v>522</v>
       </c>
       <c r="BF184" s="41" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="BG184" s="56" t="s">
         <v>524</v>
       </c>
       <c r="BH184" s="41" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="BI184" s="56" t="s">
         <v>526</v>
@@ -65493,7 +65491,7 @@
         <v>556</v>
       </c>
       <c r="H185" s="37" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="I185" s="49" t="s">
         <v>557</v>
@@ -65534,7 +65532,7 @@
         <v>552</v>
       </c>
       <c r="BF185" s="41" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="BG185" s="56" t="s">
         <v>554</v>
@@ -65560,19 +65558,19 @@
         <v>621</v>
       </c>
       <c r="CT185" s="62" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="CU185" s="63" t="s">
         <v>623</v>
       </c>
       <c r="CV185" s="62" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="CW185" s="63" t="s">
         <v>625</v>
       </c>
       <c r="CX185" s="62" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="CY185" s="63" t="s">
         <v>627</v>
@@ -65646,13 +65644,13 @@
         <v>579</v>
       </c>
       <c r="BF186" s="41" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="BG186" s="56" t="s">
         <v>581</v>
       </c>
       <c r="BH186" s="41" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="BI186" s="56" t="s">
         <v>582</v>
@@ -65672,13 +65670,13 @@
         <v>645</v>
       </c>
       <c r="CT186" s="62" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="CU186" s="63" t="s">
         <v>647</v>
       </c>
       <c r="CV186" s="62" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="CW186" s="63" t="s">
         <v>649</v>
@@ -65715,7 +65713,7 @@
         <v>605</v>
       </c>
       <c r="H187" s="37" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="I187" s="49" t="s">
         <v>607</v>
@@ -65756,7 +65754,7 @@
         <v>599</v>
       </c>
       <c r="BF187" s="41" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="BG187" s="56" t="s">
         <v>601</v>
@@ -65782,13 +65780,13 @@
         <v>655</v>
       </c>
       <c r="CT187" s="62" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="CU187" s="63" t="s">
         <v>657</v>
       </c>
       <c r="CV187" s="62" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="CW187" s="63" t="s">
         <v>659</v>
@@ -65866,13 +65864,13 @@
         <v>630</v>
       </c>
       <c r="BF188" s="41" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="BG188" s="56" t="s">
         <v>632</v>
       </c>
       <c r="BH188" s="41" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="BI188" s="56" t="s">
         <v>633</v>
@@ -65942,7 +65940,7 @@
         <v>639</v>
       </c>
       <c r="BF189" s="41" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="BG189" s="56" t="s">
         <v>639</v>
@@ -66105,25 +66103,25 @@
         <v>446</v>
       </c>
       <c r="CT191" s="70" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="CU191" s="71" t="s">
         <v>448</v>
       </c>
       <c r="CV191" s="70" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="CW191" s="71" t="s">
         <v>450</v>
       </c>
       <c r="CX191" s="70" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="CY191" s="71" t="s">
         <v>452</v>
       </c>
       <c r="CZ191" s="70" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="DA191" s="71" t="s">
         <v>454</v>
@@ -66193,7 +66191,7 @@
         <v>420</v>
       </c>
       <c r="BF192" s="41" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="BG192" s="56" t="s">
         <v>422</v>
@@ -66217,25 +66215,25 @@
         <v>473</v>
       </c>
       <c r="CT192" s="70" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="CU192" s="71" t="s">
         <v>475</v>
       </c>
       <c r="CV192" s="70" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="CW192" s="71" t="s">
         <v>477</v>
       </c>
       <c r="CX192" s="70" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="CY192" s="71" t="s">
         <v>479</v>
       </c>
       <c r="CZ192" s="70" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="DA192" s="71" t="s">
         <v>481</v>
@@ -66305,7 +66303,7 @@
         <v>458</v>
       </c>
       <c r="BF193" s="41" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="BG193" s="56" t="s">
         <v>459</v>
@@ -66329,25 +66327,25 @@
         <v>510</v>
       </c>
       <c r="CT193" s="70" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="CU193" s="71" t="s">
         <v>512</v>
       </c>
       <c r="CV193" s="70" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="CW193" s="71" t="s">
         <v>514</v>
       </c>
       <c r="CX193" s="70" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="CY193" s="71" t="s">
         <v>515</v>
       </c>
       <c r="CZ193" s="70" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="DA193" s="71" t="s">
         <v>517</v>
@@ -66376,7 +66374,7 @@
         <v>491</v>
       </c>
       <c r="H194" s="37" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="I194" s="49" t="s">
         <v>493</v>
@@ -66439,25 +66437,25 @@
         <v>541</v>
       </c>
       <c r="CT194" s="46" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="CU194" s="19" t="s">
         <v>543</v>
       </c>
       <c r="CV194" s="46" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="CW194" s="19" t="s">
         <v>545</v>
       </c>
       <c r="CX194" s="46" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="CY194" s="19" t="s">
         <v>547</v>
       </c>
       <c r="CZ194" s="46" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="DA194" s="19" t="s">
         <v>549</v>
@@ -66468,7 +66466,7 @@
         <v>522</v>
       </c>
       <c r="B195" s="21" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="C195" s="48" t="s">
         <v>524</v>
@@ -66492,7 +66490,7 @@
         <v>529</v>
       </c>
       <c r="J195" s="21" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="K195" s="48" t="s">
         <v>530</v>
@@ -66549,25 +66547,25 @@
         <v>570</v>
       </c>
       <c r="CT195" s="46" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="CU195" s="19" t="s">
         <v>572</v>
       </c>
       <c r="CV195" s="46" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="CW195" s="19" t="s">
         <v>573</v>
       </c>
       <c r="CX195" s="46" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="CY195" s="19" t="s">
         <v>575</v>
       </c>
       <c r="CZ195" s="46" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="DA195" s="19" t="s">
         <v>577</v>
@@ -66596,7 +66594,7 @@
         <v>556</v>
       </c>
       <c r="H196" s="37" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="I196" s="49" t="s">
         <v>557</v>
@@ -66659,25 +66657,25 @@
         <v>592</v>
       </c>
       <c r="CT196" s="46" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="CU196" s="19" t="s">
         <v>593</v>
       </c>
       <c r="CV196" s="46" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="CW196" s="19" t="s">
         <v>594</v>
       </c>
       <c r="CX196" s="46" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="CY196" s="19" t="s">
         <v>595</v>
       </c>
       <c r="CZ196" s="46" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="DA196" s="19" t="s">
         <v>597</v>
@@ -66769,25 +66767,25 @@
         <v>621</v>
       </c>
       <c r="CT197" s="70" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="CU197" s="71" t="s">
         <v>623</v>
       </c>
       <c r="CV197" s="70" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="CW197" s="71" t="s">
         <v>625</v>
       </c>
       <c r="CX197" s="70" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="CY197" s="71" t="s">
         <v>627</v>
       </c>
       <c r="CZ197" s="70" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="DA197" s="71" t="s">
         <v>629</v>
@@ -66816,7 +66814,7 @@
         <v>605</v>
       </c>
       <c r="H198" s="37" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="I198" s="49" t="s">
         <v>607</v>
@@ -66879,25 +66877,25 @@
         <v>645</v>
       </c>
       <c r="CT198" s="70" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="CU198" s="71" t="s">
         <v>647</v>
       </c>
       <c r="CV198" s="70" t="s">
-        <v>2030</v>
+        <v>2028</v>
       </c>
       <c r="CW198" s="71" t="s">
         <v>649</v>
       </c>
       <c r="CX198" s="70" t="s">
-        <v>2031</v>
+        <v>2029</v>
       </c>
       <c r="CY198" s="71" t="s">
         <v>651</v>
       </c>
       <c r="CZ198" s="70" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="DA198" s="71" t="s">
         <v>653</v>
@@ -66989,25 +66987,25 @@
         <v>655</v>
       </c>
       <c r="CT199" s="70" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="CU199" s="71" t="s">
         <v>657</v>
       </c>
       <c r="CV199" s="70" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="CW199" s="71" t="s">
         <v>659</v>
       </c>
       <c r="CX199" s="70" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="CY199" s="71" t="s">
         <v>661</v>
       </c>
       <c r="CZ199" s="70" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="DA199" s="71" t="s">
         <v>663</v>
@@ -67188,25 +67186,25 @@
         <v>676</v>
       </c>
       <c r="CT202" s="70" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="CU202" s="71" t="s">
         <v>678</v>
       </c>
       <c r="CV202" s="70" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="CW202" s="71" t="s">
         <v>680</v>
       </c>
       <c r="CX202" s="70" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="CY202" s="71" t="s">
         <v>949</v>
       </c>
       <c r="CZ202" s="70" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="DA202" s="71" t="s">
         <v>951</v>
@@ -67269,25 +67267,25 @@
         <v>703</v>
       </c>
       <c r="CT203" s="70" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="CU203" s="71" t="s">
         <v>704</v>
       </c>
       <c r="CV203" s="70" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="CW203" s="71" t="s">
         <v>706</v>
       </c>
       <c r="CX203" s="70" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="CY203" s="71" t="s">
         <v>963</v>
       </c>
       <c r="CZ203" s="70" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="DA203" s="71" t="s">
         <v>965</v>
@@ -67350,25 +67348,25 @@
         <v>736</v>
       </c>
       <c r="CT204" s="70" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="CU204" s="71" t="s">
         <v>738</v>
       </c>
       <c r="CV204" s="70" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="CW204" s="71" t="s">
         <v>740</v>
       </c>
       <c r="CX204" s="70" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="CY204" s="71" t="s">
         <v>978</v>
       </c>
       <c r="CZ204" s="70" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="DA204" s="71" t="s">
         <v>980</v>
@@ -67531,7 +67529,7 @@
         <v>552</v>
       </c>
       <c r="BF207" s="41" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="BG207" s="56" t="s">
         <v>554</v>
@@ -67943,13 +67941,13 @@
         <v>420</v>
       </c>
       <c r="BF214" s="41" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="BG214" s="56" t="s">
         <v>422</v>
       </c>
       <c r="BH214" s="41" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="BI214" s="56" t="s">
         <v>424</v>
@@ -67997,13 +67995,13 @@
         <v>458</v>
       </c>
       <c r="BF215" s="41" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="BG215" s="56" t="s">
         <v>459</v>
       </c>
       <c r="BH215" s="41" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="BI215" s="56" t="s">
         <v>461</v>
@@ -68051,13 +68049,13 @@
         <v>485</v>
       </c>
       <c r="BF216" s="41" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="BG216" s="56" t="s">
         <v>487</v>
       </c>
       <c r="BH216" s="41" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="BI216" s="56" t="s">
         <v>489</v>
@@ -68105,13 +68103,13 @@
         <v>522</v>
       </c>
       <c r="BF217" s="41" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="BG217" s="56" t="s">
         <v>524</v>
       </c>
       <c r="BH217" s="41" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="BI217" s="56" t="s">
         <v>526</v>
@@ -68159,13 +68157,13 @@
         <v>552</v>
       </c>
       <c r="BF218" s="41" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="BG218" s="56" t="s">
         <v>554</v>
       </c>
       <c r="BH218" s="41" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="BI218" s="56" t="s">
         <v>555</v>
@@ -68213,13 +68211,13 @@
         <v>579</v>
       </c>
       <c r="BF219" s="41" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="BG219" s="56" t="s">
         <v>581</v>
       </c>
       <c r="BH219" s="41" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="BI219" s="56" t="s">
         <v>582</v>
@@ -68262,13 +68260,13 @@
         <v>599</v>
       </c>
       <c r="BF220" s="41" t="s">
-        <v>2059</v>
+        <v>2057</v>
       </c>
       <c r="BG220" s="56" t="s">
         <v>601</v>
       </c>
       <c r="BH220" s="41" t="s">
-        <v>2060</v>
+        <v>2058</v>
       </c>
       <c r="BI220" s="56" t="s">
         <v>603</v>
@@ -68311,13 +68309,13 @@
         <v>630</v>
       </c>
       <c r="BF221" s="41" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="BG221" s="56" t="s">
         <v>632</v>
       </c>
       <c r="BH221" s="41" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="BI221" s="56" t="s">
         <v>633</v>
@@ -68360,7 +68358,7 @@
         <v>639</v>
       </c>
       <c r="BF222" s="41" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="BG222" s="56" t="s">
         <v>639</v>
@@ -68487,13 +68485,13 @@
         <v>420</v>
       </c>
       <c r="BF225" s="41" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="BG225" s="56" t="s">
         <v>422</v>
       </c>
       <c r="BH225" s="41" t="s">
-        <v>2062</v>
+        <v>2060</v>
       </c>
       <c r="BI225" s="56" t="s">
         <v>424</v>
@@ -68536,13 +68534,13 @@
         <v>458</v>
       </c>
       <c r="BF226" s="41" t="s">
-        <v>2063</v>
+        <v>2061</v>
       </c>
       <c r="BG226" s="56" t="s">
         <v>459</v>
       </c>
       <c r="BH226" s="41" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="BI226" s="56" t="s">
         <v>461</v>
@@ -68585,13 +68583,13 @@
         <v>485</v>
       </c>
       <c r="BF227" s="41" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="BG227" s="56" t="s">
         <v>487</v>
       </c>
       <c r="BH227" s="41" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="BI227" s="56" t="s">
         <v>489</v>
@@ -68634,13 +68632,13 @@
         <v>522</v>
       </c>
       <c r="BF228" s="41" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="BG228" s="56" t="s">
         <v>524</v>
       </c>
       <c r="BH228" s="41" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="BI228" s="56" t="s">
         <v>526</v>
@@ -68683,13 +68681,13 @@
         <v>552</v>
       </c>
       <c r="BF229" s="41" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="BG229" s="56" t="s">
         <v>554</v>
       </c>
       <c r="BH229" s="41" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="BI229" s="56" t="s">
         <v>555</v>
@@ -68732,13 +68730,13 @@
         <v>579</v>
       </c>
       <c r="BF230" s="41" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="BG230" s="56" t="s">
         <v>581</v>
       </c>
       <c r="BH230" s="41" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="BI230" s="56" t="s">
         <v>582</v>
@@ -68781,13 +68779,13 @@
         <v>599</v>
       </c>
       <c r="BF231" s="41" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="BG231" s="56" t="s">
         <v>601</v>
       </c>
       <c r="BH231" s="41" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="BI231" s="56" t="s">
         <v>603</v>
@@ -68830,13 +68828,13 @@
         <v>630</v>
       </c>
       <c r="BF232" s="41" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="BG232" s="56" t="s">
         <v>632</v>
       </c>
       <c r="BH232" s="41" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="BI232" s="56" t="s">
         <v>633</v>
@@ -68879,7 +68877,7 @@
         <v>639</v>
       </c>
       <c r="BF233" s="41" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="BG233" s="56" t="s">
         <v>639</v>
@@ -69006,13 +69004,13 @@
         <v>420</v>
       </c>
       <c r="BF236" s="41" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="BG236" s="56" t="s">
         <v>422</v>
       </c>
       <c r="BH236" s="41" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="BI236" s="56" t="s">
         <v>424</v>
@@ -69055,13 +69053,13 @@
         <v>458</v>
       </c>
       <c r="BF237" s="41" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="BG237" s="56" t="s">
         <v>459</v>
       </c>
       <c r="BH237" s="41" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="BI237" s="56" t="s">
         <v>461</v>
@@ -69104,13 +69102,13 @@
         <v>485</v>
       </c>
       <c r="BF238" s="41" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="BG238" s="56" t="s">
         <v>487</v>
       </c>
       <c r="BH238" s="41" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="BI238" s="56" t="s">
         <v>489</v>
@@ -69153,13 +69151,13 @@
         <v>522</v>
       </c>
       <c r="BF239" s="41" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="BG239" s="56" t="s">
         <v>524</v>
       </c>
       <c r="BH239" s="41" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="BI239" s="56" t="s">
         <v>526</v>
@@ -69202,13 +69200,13 @@
         <v>552</v>
       </c>
       <c r="BF240" s="41" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="BG240" s="56" t="s">
         <v>554</v>
       </c>
       <c r="BH240" s="41" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="BI240" s="56" t="s">
         <v>555</v>
@@ -69251,13 +69249,13 @@
         <v>579</v>
       </c>
       <c r="BF241" s="41" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="BG241" s="56" t="s">
         <v>581</v>
       </c>
       <c r="BH241" s="41" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="BI241" s="56" t="s">
         <v>582</v>
@@ -69300,13 +69298,13 @@
         <v>599</v>
       </c>
       <c r="BF242" s="41" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="BG242" s="56" t="s">
         <v>601</v>
       </c>
       <c r="BH242" s="41" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="BI242" s="56" t="s">
         <v>603</v>
@@ -69349,13 +69347,13 @@
         <v>630</v>
       </c>
       <c r="BF243" s="41" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="BG243" s="56" t="s">
         <v>632</v>
       </c>
       <c r="BH243" s="41" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="BI243" s="56" t="s">
         <v>633</v>
@@ -69398,7 +69396,7 @@
         <v>639</v>
       </c>
       <c r="BF244" s="41" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="BG244" s="56" t="s">
         <v>639</v>
@@ -69868,7 +69866,7 @@
         <v>630</v>
       </c>
       <c r="BF254" s="41" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="BG254" s="56" t="s">
         <v>632</v>
@@ -70091,7 +70089,7 @@
         <v>458</v>
       </c>
       <c r="BF259" s="41" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="BG259" s="56" t="s">
         <v>459</v>
@@ -70183,7 +70181,7 @@
         <v>522</v>
       </c>
       <c r="BF261" s="41" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="BG261" s="56" t="s">
         <v>524</v>
@@ -70262,7 +70260,7 @@
         <v>579</v>
       </c>
       <c r="BF263" s="41" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="BG263" s="56" t="s">
         <v>581</v>
@@ -70299,7 +70297,7 @@
         <v>599</v>
       </c>
       <c r="BF264" s="41" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="BG264" s="56" t="s">
         <v>601</v>
@@ -70470,13 +70468,13 @@
         <v>420</v>
       </c>
       <c r="BF269" s="41" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="BG269" s="56" t="s">
         <v>422</v>
       </c>
       <c r="BH269" s="41" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="BI269" s="56" t="s">
         <v>424</v>
@@ -70509,13 +70507,13 @@
         <v>458</v>
       </c>
       <c r="BF270" s="41" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="BG270" s="56" t="s">
         <v>459</v>
       </c>
       <c r="BH270" s="41" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="BI270" s="56" t="s">
         <v>461</v>
@@ -70548,13 +70546,13 @@
         <v>485</v>
       </c>
       <c r="BF271" s="41" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="BG271" s="56" t="s">
         <v>487</v>
       </c>
       <c r="BH271" s="41" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="BI271" s="56" t="s">
         <v>489</v>
@@ -70587,13 +70585,13 @@
         <v>522</v>
       </c>
       <c r="BF272" s="41" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="BG272" s="56" t="s">
         <v>524</v>
       </c>
       <c r="BH272" s="41" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="BI272" s="56" t="s">
         <v>526</v>
@@ -70626,13 +70624,13 @@
         <v>552</v>
       </c>
       <c r="BF273" s="41" t="s">
-        <v>2098</v>
+        <v>2096</v>
       </c>
       <c r="BG273" s="56" t="s">
         <v>554</v>
       </c>
       <c r="BH273" s="41" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="BI273" s="56" t="s">
         <v>555</v>
@@ -70665,13 +70663,13 @@
         <v>579</v>
       </c>
       <c r="BF274" s="41" t="s">
-        <v>2099</v>
+        <v>2097</v>
       </c>
       <c r="BG274" s="56" t="s">
         <v>581</v>
       </c>
       <c r="BH274" s="41" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="BI274" s="56" t="s">
         <v>582</v>
@@ -70704,13 +70702,13 @@
         <v>599</v>
       </c>
       <c r="BF275" s="41" t="s">
-        <v>2100</v>
+        <v>2098</v>
       </c>
       <c r="BG275" s="56" t="s">
         <v>601</v>
       </c>
       <c r="BH275" s="41" t="s">
-        <v>2101</v>
+        <v>2099</v>
       </c>
       <c r="BI275" s="56" t="s">
         <v>603</v>
@@ -70743,13 +70741,13 @@
         <v>630</v>
       </c>
       <c r="BF276" s="41" t="s">
-        <v>2102</v>
+        <v>2100</v>
       </c>
       <c r="BG276" s="56" t="s">
         <v>632</v>
       </c>
       <c r="BH276" s="41" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="BI276" s="56" t="s">
         <v>633</v>
@@ -70782,7 +70780,7 @@
         <v>639</v>
       </c>
       <c r="BF277" s="41" t="s">
-        <v>2103</v>
+        <v>2101</v>
       </c>
       <c r="BG277" s="56" t="s">
         <v>639</v>
@@ -70975,7 +70973,7 @@
         <v>522</v>
       </c>
       <c r="BF283" s="41" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="BG283" s="56" t="s">
         <v>524</v>
@@ -71021,7 +71019,7 @@
         <v>579</v>
       </c>
       <c r="BF285" s="41" t="s">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="BG285" s="56" t="s">
         <v>581</v>
@@ -71678,46 +71676,46 @@
   <sheetData>
     <row r="1" s="22" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="22" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C1" s="82" t="s">
         <v>2105</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="D1" s="82" t="s">
         <v>2106</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="E1" s="22" t="s">
         <v>2107</v>
       </c>
-      <c r="D1" s="82" t="s">
+      <c r="F1" s="22" t="s">
         <v>2108</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="G1" s="22" t="s">
         <v>2109</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="H1" s="82" t="s">
         <v>2110</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>2111</v>
       </c>
-      <c r="H1" s="82" t="s">
+      <c r="J1" s="82" t="s">
         <v>2112</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="K1" s="82" t="s">
         <v>2113</v>
       </c>
-      <c r="J1" s="82" t="s">
+      <c r="L1" s="82" t="s">
         <v>2114</v>
       </c>
-      <c r="K1" s="82" t="s">
+      <c r="M1" s="82" t="s">
         <v>2115</v>
       </c>
-      <c r="L1" s="82" t="s">
+      <c r="N1" s="82" t="s">
         <v>2116</v>
-      </c>
-      <c r="M1" s="82" t="s">
-        <v>2117</v>
-      </c>
-      <c r="N1" s="82" t="s">
-        <v>2118</v>
       </c>
       <c r="AMI1" s="20"/>
       <c r="AMJ1" s="20"/>
@@ -71727,40 +71725,40 @@
         <v>420</v>
       </c>
       <c r="B2" s="83" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C2" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E2" s="84" t="s">
+        <v>2118</v>
+      </c>
+      <c r="F2" s="84" t="s">
         <v>2119</v>
       </c>
-      <c r="C2" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E2" s="84" t="s">
+      <c r="G2" s="84" t="s">
         <v>2120</v>
       </c>
-      <c r="F2" s="84" t="s">
+      <c r="H2" s="84" t="s">
         <v>2121</v>
       </c>
-      <c r="G2" s="84" t="s">
+      <c r="I2" s="83" t="s">
         <v>2122</v>
       </c>
-      <c r="H2" s="84" t="s">
+      <c r="J2" s="83" t="s">
         <v>2123</v>
       </c>
-      <c r="I2" s="83" t="s">
+      <c r="K2" s="84" t="s">
         <v>2124</v>
       </c>
-      <c r="J2" s="83" t="s">
+      <c r="L2" s="84" t="s">
         <v>2125</v>
       </c>
-      <c r="K2" s="84" t="s">
+      <c r="M2" s="84" t="s">
         <v>2126</v>
       </c>
-      <c r="L2" s="84" t="s">
+      <c r="N2" s="84" t="s">
         <v>2127</v>
-      </c>
-      <c r="M2" s="84" t="s">
-        <v>2128</v>
-      </c>
-      <c r="N2" s="84" t="s">
-        <v>2129</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71768,40 +71766,40 @@
         <v>458</v>
       </c>
       <c r="B3" s="83" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C3" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E3" s="84" t="s">
+        <v>2129</v>
+      </c>
+      <c r="F3" s="84" t="s">
         <v>2130</v>
       </c>
-      <c r="C3" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E3" s="84" t="s">
+      <c r="G3" s="84" t="s">
         <v>2131</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="H3" s="84" t="s">
         <v>2132</v>
       </c>
-      <c r="G3" s="84" t="s">
+      <c r="I3" s="83" t="s">
         <v>2133</v>
       </c>
-      <c r="H3" s="84" t="s">
+      <c r="J3" s="83" t="s">
         <v>2134</v>
       </c>
-      <c r="I3" s="83" t="s">
+      <c r="K3" s="84" t="s">
         <v>2135</v>
       </c>
-      <c r="J3" s="83" t="s">
+      <c r="L3" s="84" t="s">
         <v>2136</v>
       </c>
-      <c r="K3" s="84" t="s">
+      <c r="M3" s="84" t="s">
         <v>2137</v>
       </c>
-      <c r="L3" s="84" t="s">
+      <c r="N3" s="84" t="s">
         <v>2138</v>
-      </c>
-      <c r="M3" s="84" t="s">
-        <v>2139</v>
-      </c>
-      <c r="N3" s="84" t="s">
-        <v>2140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71809,40 +71807,40 @@
         <v>485</v>
       </c>
       <c r="B4" s="83" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C4" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E4" s="84" t="s">
+        <v>2140</v>
+      </c>
+      <c r="F4" s="84" t="s">
         <v>2141</v>
       </c>
-      <c r="C4" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E4" s="84" t="s">
+      <c r="G4" s="84" t="s">
         <v>2142</v>
       </c>
-      <c r="F4" s="84" t="s">
+      <c r="H4" s="84" t="s">
         <v>2143</v>
       </c>
-      <c r="G4" s="84" t="s">
+      <c r="I4" s="83" t="s">
         <v>2144</v>
       </c>
-      <c r="H4" s="84" t="s">
+      <c r="J4" s="83" t="s">
         <v>2145</v>
       </c>
-      <c r="I4" s="83" t="s">
+      <c r="K4" s="84" t="s">
         <v>2146</v>
       </c>
-      <c r="J4" s="83" t="s">
+      <c r="L4" s="84" t="s">
         <v>2147</v>
       </c>
-      <c r="K4" s="84" t="s">
+      <c r="M4" s="84" t="s">
         <v>2148</v>
       </c>
-      <c r="L4" s="84" t="s">
+      <c r="N4" s="84" t="s">
         <v>2149</v>
-      </c>
-      <c r="M4" s="84" t="s">
-        <v>2150</v>
-      </c>
-      <c r="N4" s="84" t="s">
-        <v>2151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71850,40 +71848,40 @@
         <v>522</v>
       </c>
       <c r="B5" s="83" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C5" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E5" s="84" t="s">
+        <v>2151</v>
+      </c>
+      <c r="F5" s="84" t="s">
         <v>2152</v>
       </c>
-      <c r="C5" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E5" s="84" t="s">
+      <c r="G5" s="84" t="s">
         <v>2153</v>
       </c>
-      <c r="F5" s="84" t="s">
+      <c r="H5" s="84" t="s">
         <v>2154</v>
       </c>
-      <c r="G5" s="84" t="s">
+      <c r="I5" s="83" t="s">
         <v>2155</v>
       </c>
-      <c r="H5" s="84" t="s">
+      <c r="J5" s="83" t="s">
         <v>2156</v>
       </c>
-      <c r="I5" s="83" t="s">
+      <c r="K5" s="84" t="s">
         <v>2157</v>
       </c>
-      <c r="J5" s="83" t="s">
+      <c r="L5" s="84" t="s">
         <v>2158</v>
       </c>
-      <c r="K5" s="84" t="s">
+      <c r="M5" s="84" t="s">
         <v>2159</v>
       </c>
-      <c r="L5" s="84" t="s">
+      <c r="N5" s="84" t="s">
         <v>2160</v>
-      </c>
-      <c r="M5" s="84" t="s">
-        <v>2161</v>
-      </c>
-      <c r="N5" s="84" t="s">
-        <v>2162</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71891,40 +71889,40 @@
         <v>552</v>
       </c>
       <c r="B6" s="83" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C6" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E6" s="84" t="s">
+        <v>2162</v>
+      </c>
+      <c r="F6" s="84" t="s">
         <v>2163</v>
       </c>
-      <c r="C6" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E6" s="84" t="s">
+      <c r="G6" s="84" t="s">
         <v>2164</v>
       </c>
-      <c r="F6" s="84" t="s">
+      <c r="H6" s="84" t="s">
         <v>2165</v>
       </c>
-      <c r="G6" s="84" t="s">
+      <c r="I6" s="83" t="s">
         <v>2166</v>
       </c>
-      <c r="H6" s="84" t="s">
+      <c r="J6" s="83" t="s">
         <v>2167</v>
       </c>
-      <c r="I6" s="83" t="s">
+      <c r="K6" s="84" t="s">
         <v>2168</v>
       </c>
-      <c r="J6" s="83" t="s">
+      <c r="L6" s="84" t="s">
         <v>2169</v>
       </c>
-      <c r="K6" s="84" t="s">
+      <c r="M6" s="84" t="s">
         <v>2170</v>
       </c>
-      <c r="L6" s="84" t="s">
+      <c r="N6" s="84" t="s">
         <v>2171</v>
-      </c>
-      <c r="M6" s="84" t="s">
-        <v>2172</v>
-      </c>
-      <c r="N6" s="84" t="s">
-        <v>2173</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71932,40 +71930,40 @@
         <v>579</v>
       </c>
       <c r="B7" s="83" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C7" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E7" s="84" t="s">
+        <v>2173</v>
+      </c>
+      <c r="F7" s="84" t="s">
         <v>2174</v>
       </c>
-      <c r="C7" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E7" s="84" t="s">
+      <c r="G7" s="84" t="s">
         <v>2175</v>
       </c>
-      <c r="F7" s="84" t="s">
+      <c r="H7" s="84" t="s">
         <v>2176</v>
       </c>
-      <c r="G7" s="84" t="s">
+      <c r="I7" s="83" t="s">
         <v>2177</v>
       </c>
-      <c r="H7" s="84" t="s">
+      <c r="J7" s="83" t="s">
         <v>2178</v>
       </c>
-      <c r="I7" s="83" t="s">
+      <c r="K7" s="84" t="s">
         <v>2179</v>
       </c>
-      <c r="J7" s="83" t="s">
+      <c r="L7" s="84" t="s">
         <v>2180</v>
       </c>
-      <c r="K7" s="84" t="s">
+      <c r="M7" s="84" t="s">
         <v>2181</v>
       </c>
-      <c r="L7" s="84" t="s">
+      <c r="N7" s="84" t="s">
         <v>2182</v>
-      </c>
-      <c r="M7" s="84" t="s">
-        <v>2183</v>
-      </c>
-      <c r="N7" s="84" t="s">
-        <v>2184</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -71973,40 +71971,40 @@
         <v>599</v>
       </c>
       <c r="B8" s="83" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C8" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E8" s="84" t="s">
+        <v>2184</v>
+      </c>
+      <c r="F8" s="84" t="s">
         <v>2185</v>
       </c>
-      <c r="C8" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E8" s="84" t="s">
+      <c r="G8" s="84" t="s">
         <v>2186</v>
       </c>
-      <c r="F8" s="84" t="s">
+      <c r="H8" s="84" t="s">
         <v>2187</v>
       </c>
-      <c r="G8" s="84" t="s">
+      <c r="I8" s="83" t="s">
         <v>2188</v>
       </c>
-      <c r="H8" s="84" t="s">
+      <c r="J8" s="83" t="s">
         <v>2189</v>
       </c>
-      <c r="I8" s="83" t="s">
+      <c r="K8" s="84" t="s">
         <v>2190</v>
       </c>
-      <c r="J8" s="83" t="s">
+      <c r="L8" s="84" t="s">
         <v>2191</v>
       </c>
-      <c r="K8" s="84" t="s">
+      <c r="M8" s="84" t="s">
         <v>2192</v>
       </c>
-      <c r="L8" s="84" t="s">
+      <c r="N8" s="84" t="s">
         <v>2193</v>
-      </c>
-      <c r="M8" s="84" t="s">
-        <v>2194</v>
-      </c>
-      <c r="N8" s="84" t="s">
-        <v>2195</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -72014,40 +72012,40 @@
         <v>630</v>
       </c>
       <c r="B9" s="83" t="s">
+        <v>2194</v>
+      </c>
+      <c r="C9" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E9" s="84" t="s">
+        <v>2195</v>
+      </c>
+      <c r="F9" s="84" t="s">
         <v>2196</v>
       </c>
-      <c r="C9" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E9" s="84" t="s">
+      <c r="G9" s="84" t="s">
         <v>2197</v>
       </c>
-      <c r="F9" s="84" t="s">
+      <c r="H9" s="84" t="s">
         <v>2198</v>
       </c>
-      <c r="G9" s="84" t="s">
+      <c r="I9" s="83" t="s">
         <v>2199</v>
       </c>
-      <c r="H9" s="84" t="s">
+      <c r="J9" s="83" t="s">
         <v>2200</v>
       </c>
-      <c r="I9" s="83" t="s">
+      <c r="K9" s="84" t="s">
         <v>2201</v>
       </c>
-      <c r="J9" s="83" t="s">
+      <c r="L9" s="84" t="s">
         <v>2202</v>
       </c>
-      <c r="K9" s="84" t="s">
+      <c r="M9" s="84" t="s">
         <v>2203</v>
       </c>
-      <c r="L9" s="84" t="s">
+      <c r="N9" s="84" t="s">
         <v>2204</v>
-      </c>
-      <c r="M9" s="84" t="s">
-        <v>2205</v>
-      </c>
-      <c r="N9" s="84" t="s">
-        <v>2206</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -72055,202 +72053,202 @@
         <v>639</v>
       </c>
       <c r="B10" s="83" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E10" s="84" t="s">
+        <v>2206</v>
+      </c>
+      <c r="F10" s="84" t="s">
+        <v>2206</v>
+      </c>
+      <c r="G10" s="84" t="s">
         <v>2207</v>
       </c>
-      <c r="E10" s="84" t="s">
+      <c r="H10" s="84" t="s">
         <v>2208</v>
       </c>
-      <c r="F10" s="84" t="s">
-        <v>2208</v>
-      </c>
-      <c r="G10" s="84" t="s">
+      <c r="I10" s="83" t="s">
         <v>2209</v>
       </c>
-      <c r="H10" s="84" t="s">
+      <c r="J10" s="83" t="s">
         <v>2210</v>
       </c>
-      <c r="I10" s="83" t="s">
+      <c r="K10" s="84" t="s">
         <v>2211</v>
       </c>
-      <c r="J10" s="83" t="s">
+      <c r="L10" s="84" t="s">
+        <v>2211</v>
+      </c>
+      <c r="M10" s="84" t="s">
         <v>2212</v>
       </c>
-      <c r="K10" s="84" t="s">
+      <c r="N10" s="84" t="s">
         <v>2213</v>
-      </c>
-      <c r="L10" s="84" t="s">
-        <v>2213</v>
-      </c>
-      <c r="M10" s="84" t="s">
-        <v>2214</v>
-      </c>
-      <c r="N10" s="84" t="s">
-        <v>2215</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="83" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B12" s="83" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C12" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E12" s="84" t="s">
         <v>2216</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="F12" s="84" t="s">
         <v>2217</v>
       </c>
-      <c r="C12" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E12" s="84" t="s">
+      <c r="G12" s="84" t="s">
         <v>2218</v>
       </c>
-      <c r="F12" s="84" t="s">
+      <c r="H12" s="84" t="s">
         <v>2219</v>
       </c>
-      <c r="G12" s="84" t="s">
+      <c r="I12" s="83" t="s">
         <v>2220</v>
       </c>
-      <c r="H12" s="84" t="s">
+      <c r="J12" s="83" t="s">
         <v>2221</v>
       </c>
-      <c r="I12" s="83" t="s">
+      <c r="K12" s="84" t="s">
         <v>2222</v>
       </c>
-      <c r="J12" s="83" t="s">
+      <c r="L12" s="84" t="s">
         <v>2223</v>
       </c>
-      <c r="K12" s="84" t="s">
+      <c r="M12" s="84" t="s">
         <v>2224</v>
       </c>
-      <c r="L12" s="84" t="s">
+      <c r="N12" s="84" t="s">
         <v>2225</v>
-      </c>
-      <c r="M12" s="84" t="s">
-        <v>2226</v>
-      </c>
-      <c r="N12" s="84" t="s">
-        <v>2227</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="83" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B13" s="83" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C13" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E13" s="84" t="s">
         <v>2228</v>
       </c>
-      <c r="B13" s="83" t="s">
+      <c r="F13" s="84" t="s">
         <v>2229</v>
       </c>
-      <c r="C13" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E13" s="84" t="s">
+      <c r="G13" s="84" t="s">
         <v>2230</v>
       </c>
-      <c r="F13" s="84" t="s">
+      <c r="H13" s="84" t="s">
         <v>2231</v>
       </c>
-      <c r="G13" s="84" t="s">
+      <c r="I13" s="83" t="s">
         <v>2232</v>
       </c>
-      <c r="H13" s="84" t="s">
+      <c r="J13" s="83" t="s">
         <v>2233</v>
       </c>
-      <c r="I13" s="83" t="s">
+      <c r="K13" s="84" t="s">
         <v>2234</v>
       </c>
-      <c r="J13" s="83" t="s">
+      <c r="L13" s="84" t="s">
         <v>2235</v>
       </c>
-      <c r="K13" s="84" t="s">
+      <c r="M13" s="84" t="s">
         <v>2236</v>
       </c>
-      <c r="L13" s="84" t="s">
+      <c r="N13" s="84" t="s">
         <v>2237</v>
-      </c>
-      <c r="M13" s="84" t="s">
-        <v>2238</v>
-      </c>
-      <c r="N13" s="84" t="s">
-        <v>2239</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="83" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B14" s="83" t="s">
+        <v>2239</v>
+      </c>
+      <c r="C14" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E14" s="84" t="s">
         <v>2240</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="F14" s="84" t="s">
         <v>2241</v>
       </c>
-      <c r="C14" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E14" s="84" t="s">
+      <c r="G14" s="84" t="s">
         <v>2242</v>
       </c>
-      <c r="F14" s="84" t="s">
+      <c r="H14" s="84" t="s">
         <v>2243</v>
       </c>
-      <c r="G14" s="84" t="s">
+      <c r="I14" s="83" t="s">
         <v>2244</v>
       </c>
-      <c r="H14" s="84" t="s">
+      <c r="J14" s="83" t="s">
         <v>2245</v>
       </c>
-      <c r="I14" s="83" t="s">
+      <c r="K14" s="84" t="s">
         <v>2246</v>
       </c>
-      <c r="J14" s="83" t="s">
+      <c r="L14" s="84" t="s">
         <v>2247</v>
       </c>
-      <c r="K14" s="84" t="s">
+      <c r="M14" s="84" t="s">
         <v>2248</v>
       </c>
-      <c r="L14" s="84" t="s">
+      <c r="N14" s="84" t="s">
         <v>2249</v>
-      </c>
-      <c r="M14" s="84" t="s">
-        <v>2250</v>
-      </c>
-      <c r="N14" s="84" t="s">
-        <v>2251</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="83" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B15" s="83" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C15" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E15" s="84" t="s">
         <v>2252</v>
       </c>
-      <c r="B15" s="83" t="s">
+      <c r="F15" s="84" t="s">
+        <v>2252</v>
+      </c>
+      <c r="G15" s="84" t="s">
         <v>2253</v>
       </c>
-      <c r="C15" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E15" s="84" t="s">
+      <c r="H15" s="84" t="s">
         <v>2254</v>
       </c>
-      <c r="F15" s="84" t="s">
-        <v>2254</v>
-      </c>
-      <c r="G15" s="84" t="s">
+      <c r="I15" s="83" t="s">
         <v>2255</v>
       </c>
-      <c r="H15" s="84" t="s">
+      <c r="J15" s="83" t="s">
         <v>2256</v>
       </c>
-      <c r="I15" s="83" t="s">
+      <c r="K15" s="84" t="s">
         <v>2257</v>
       </c>
-      <c r="J15" s="83" t="s">
+      <c r="L15" s="84" t="s">
+        <v>2257</v>
+      </c>
+      <c r="M15" s="84" t="s">
         <v>2258</v>
       </c>
-      <c r="K15" s="84" t="s">
+      <c r="N15" s="84" t="s">
         <v>2259</v>
-      </c>
-      <c r="L15" s="84" t="s">
-        <v>2259</v>
-      </c>
-      <c r="M15" s="84" t="s">
-        <v>2260</v>
-      </c>
-      <c r="N15" s="84" t="s">
-        <v>2261</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -72259,40 +72257,40 @@
         <v>416</v>
       </c>
       <c r="B17" s="83" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C17" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E17" s="84" t="s">
+        <v>2261</v>
+      </c>
+      <c r="F17" s="84" t="s">
         <v>2262</v>
       </c>
-      <c r="C17" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E17" s="84" t="s">
+      <c r="G17" s="84" t="s">
         <v>2263</v>
       </c>
-      <c r="F17" s="84" t="s">
+      <c r="H17" s="84" t="s">
         <v>2264</v>
       </c>
-      <c r="G17" s="84" t="s">
+      <c r="I17" s="83" t="s">
         <v>2265</v>
       </c>
-      <c r="H17" s="84" t="s">
+      <c r="J17" s="83" t="s">
         <v>2266</v>
       </c>
-      <c r="I17" s="83" t="s">
+      <c r="K17" s="84" t="s">
         <v>2267</v>
       </c>
-      <c r="J17" s="83" t="s">
+      <c r="L17" s="84" t="s">
         <v>2268</v>
       </c>
-      <c r="K17" s="84" t="s">
+      <c r="M17" s="84" t="s">
         <v>2269</v>
       </c>
-      <c r="L17" s="84" t="s">
+      <c r="N17" s="84" t="s">
         <v>2270</v>
-      </c>
-      <c r="M17" s="84" t="s">
-        <v>2271</v>
-      </c>
-      <c r="N17" s="84" t="s">
-        <v>2272</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -72300,40 +72298,40 @@
         <v>417</v>
       </c>
       <c r="B18" s="83" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C18" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E18" s="84" t="s">
+        <v>2272</v>
+      </c>
+      <c r="F18" s="84" t="s">
         <v>2273</v>
       </c>
-      <c r="C18" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E18" s="84" t="s">
+      <c r="G18" s="84" t="s">
         <v>2274</v>
       </c>
-      <c r="F18" s="84" t="s">
+      <c r="H18" s="84" t="s">
         <v>2275</v>
       </c>
-      <c r="G18" s="84" t="s">
+      <c r="I18" s="83" t="s">
         <v>2276</v>
       </c>
-      <c r="H18" s="84" t="s">
+      <c r="J18" s="83" t="s">
         <v>2277</v>
       </c>
-      <c r="I18" s="83" t="s">
+      <c r="K18" s="84" t="s">
         <v>2278</v>
       </c>
-      <c r="J18" s="83" t="s">
+      <c r="L18" s="84" t="s">
         <v>2279</v>
       </c>
-      <c r="K18" s="84" t="s">
+      <c r="M18" s="84" t="s">
         <v>2280</v>
       </c>
-      <c r="L18" s="84" t="s">
+      <c r="N18" s="84" t="s">
         <v>2281</v>
-      </c>
-      <c r="M18" s="84" t="s">
-        <v>2282</v>
-      </c>
-      <c r="N18" s="84" t="s">
-        <v>2283</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -72344,597 +72342,597 @@
         <v>1305</v>
       </c>
       <c r="C19" s="83" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="E19" s="84" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F19" s="84" t="s">
+        <v>2283</v>
+      </c>
+      <c r="G19" s="84" t="s">
         <v>2284</v>
       </c>
-      <c r="F19" s="84" t="s">
+      <c r="H19" s="84" t="s">
         <v>2285</v>
       </c>
-      <c r="G19" s="84" t="s">
+      <c r="I19" s="83" t="s">
         <v>2286</v>
       </c>
-      <c r="H19" s="84" t="s">
+      <c r="J19" s="83" t="s">
         <v>2287</v>
       </c>
-      <c r="I19" s="83" t="s">
+      <c r="K19" s="84" t="s">
         <v>2288</v>
       </c>
-      <c r="J19" s="83" t="s">
+      <c r="L19" s="84" t="s">
         <v>2289</v>
       </c>
-      <c r="K19" s="84" t="s">
+      <c r="M19" s="84" t="s">
         <v>2290</v>
       </c>
-      <c r="L19" s="84" t="s">
+      <c r="N19" s="84" t="s">
         <v>2291</v>
-      </c>
-      <c r="M19" s="84" t="s">
-        <v>2292</v>
-      </c>
-      <c r="N19" s="84" t="s">
-        <v>2293</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="83" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B21" s="83" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C21" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E21" s="84" t="s">
         <v>2294</v>
       </c>
-      <c r="B21" s="83" t="s">
+      <c r="F21" s="84" t="s">
         <v>2295</v>
       </c>
-      <c r="C21" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E21" s="84" t="s">
+      <c r="G21" s="84" t="s">
         <v>2296</v>
       </c>
-      <c r="F21" s="84" t="s">
+      <c r="H21" s="84" t="s">
         <v>2297</v>
       </c>
-      <c r="G21" s="84" t="s">
+      <c r="I21" s="83" t="s">
         <v>2298</v>
       </c>
-      <c r="H21" s="84" t="s">
+      <c r="J21" s="83" t="s">
         <v>2299</v>
       </c>
-      <c r="I21" s="83" t="s">
+      <c r="K21" s="84" t="s">
         <v>2300</v>
       </c>
-      <c r="J21" s="83" t="s">
+      <c r="L21" s="84" t="s">
         <v>2301</v>
       </c>
-      <c r="K21" s="84" t="s">
+      <c r="M21" s="84" t="s">
         <v>2302</v>
       </c>
-      <c r="L21" s="84" t="s">
+      <c r="N21" s="84" t="s">
         <v>2303</v>
-      </c>
-      <c r="M21" s="84" t="s">
-        <v>2304</v>
-      </c>
-      <c r="N21" s="84" t="s">
-        <v>2305</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="83" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B22" s="83" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C22" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E22" s="84" t="s">
         <v>2306</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="F22" s="84" t="s">
         <v>2307</v>
       </c>
-      <c r="C22" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E22" s="84" t="s">
+      <c r="G22" s="84" t="s">
         <v>2308</v>
       </c>
-      <c r="F22" s="84" t="s">
+      <c r="H22" s="84" t="s">
         <v>2309</v>
       </c>
-      <c r="G22" s="84" t="s">
+      <c r="I22" s="83" t="s">
         <v>2310</v>
       </c>
-      <c r="H22" s="84" t="s">
+      <c r="J22" s="83" t="s">
         <v>2311</v>
       </c>
-      <c r="I22" s="83" t="s">
+      <c r="K22" s="84" t="s">
         <v>2312</v>
       </c>
-      <c r="J22" s="83" t="s">
+      <c r="L22" s="84" t="s">
         <v>2313</v>
       </c>
-      <c r="K22" s="84" t="s">
+      <c r="M22" s="84" t="s">
         <v>2314</v>
       </c>
-      <c r="L22" s="84" t="s">
+      <c r="N22" s="84" t="s">
         <v>2315</v>
-      </c>
-      <c r="M22" s="84" t="s">
-        <v>2316</v>
-      </c>
-      <c r="N22" s="84" t="s">
-        <v>2317</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="83" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B24" s="83" t="s">
+        <v>2317</v>
+      </c>
+      <c r="C24" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D24" s="83" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E24" s="84" t="s">
         <v>2318</v>
       </c>
-      <c r="B24" s="83" t="s">
+      <c r="F24" s="84" t="s">
         <v>2319</v>
       </c>
-      <c r="C24" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D24" s="83" t="s">
-        <v>2108</v>
-      </c>
-      <c r="E24" s="84" t="s">
+      <c r="G24" s="84" t="s">
         <v>2320</v>
       </c>
-      <c r="F24" s="84" t="s">
+      <c r="H24" s="84" t="s">
         <v>2321</v>
       </c>
-      <c r="G24" s="84" t="s">
+      <c r="I24" s="83" t="s">
         <v>2322</v>
       </c>
-      <c r="H24" s="84" t="s">
+      <c r="J24" s="83" t="s">
         <v>2323</v>
       </c>
-      <c r="I24" s="83" t="s">
+      <c r="K24" s="84" t="s">
         <v>2324</v>
       </c>
-      <c r="J24" s="83" t="s">
+      <c r="L24" s="84" t="s">
         <v>2325</v>
       </c>
-      <c r="K24" s="84" t="s">
+      <c r="M24" s="84" t="s">
         <v>2326</v>
       </c>
-      <c r="L24" s="84" t="s">
+      <c r="N24" s="84" t="s">
         <v>2327</v>
-      </c>
-      <c r="M24" s="84" t="s">
-        <v>2328</v>
-      </c>
-      <c r="N24" s="84" t="s">
-        <v>2329</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="83" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B25" s="83" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C25" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D25" s="83" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E25" s="84" t="s">
         <v>2330</v>
       </c>
-      <c r="B25" s="83" t="s">
+      <c r="F25" s="84" t="s">
         <v>2331</v>
       </c>
-      <c r="C25" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D25" s="83" t="s">
-        <v>2108</v>
-      </c>
-      <c r="E25" s="84" t="s">
+      <c r="G25" s="84" t="s">
         <v>2332</v>
       </c>
-      <c r="F25" s="84" t="s">
+      <c r="H25" s="84" t="s">
         <v>2333</v>
       </c>
-      <c r="G25" s="84" t="s">
+      <c r="I25" s="83" t="s">
         <v>2334</v>
       </c>
-      <c r="H25" s="84" t="s">
+      <c r="J25" s="83" t="s">
         <v>2335</v>
       </c>
-      <c r="I25" s="83" t="s">
+      <c r="K25" s="84" t="s">
         <v>2336</v>
       </c>
-      <c r="J25" s="83" t="s">
+      <c r="L25" s="84" t="s">
         <v>2337</v>
       </c>
-      <c r="K25" s="84" t="s">
+      <c r="M25" s="84" t="s">
         <v>2338</v>
       </c>
-      <c r="L25" s="84" t="s">
+      <c r="N25" s="84" t="s">
         <v>2339</v>
-      </c>
-      <c r="M25" s="84" t="s">
-        <v>2340</v>
-      </c>
-      <c r="N25" s="84" t="s">
-        <v>2341</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="83" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B26" s="83" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C26" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D26" s="83" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E26" s="84" t="s">
         <v>2342</v>
       </c>
-      <c r="B26" s="83" t="s">
+      <c r="F26" s="84" t="s">
         <v>2343</v>
       </c>
-      <c r="C26" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D26" s="83" t="s">
-        <v>2108</v>
-      </c>
-      <c r="E26" s="84" t="s">
+      <c r="G26" s="84" t="s">
         <v>2344</v>
       </c>
-      <c r="F26" s="84" t="s">
+      <c r="H26" s="84" t="s">
         <v>2345</v>
       </c>
-      <c r="G26" s="84" t="s">
+      <c r="I26" s="83" t="s">
         <v>2346</v>
       </c>
-      <c r="H26" s="84" t="s">
+      <c r="J26" s="83" t="s">
         <v>2347</v>
       </c>
-      <c r="I26" s="83" t="s">
+      <c r="K26" s="84" t="s">
         <v>2348</v>
       </c>
-      <c r="J26" s="83" t="s">
+      <c r="L26" s="84" t="s">
         <v>2349</v>
       </c>
-      <c r="K26" s="84" t="s">
+      <c r="M26" s="84" t="s">
         <v>2350</v>
       </c>
-      <c r="L26" s="84" t="s">
+      <c r="N26" s="84" t="s">
         <v>2351</v>
-      </c>
-      <c r="M26" s="84" t="s">
-        <v>2352</v>
-      </c>
-      <c r="N26" s="84" t="s">
-        <v>2353</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="83" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B27" s="83" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C27" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D27" s="83" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E27" s="84" t="s">
         <v>2354</v>
       </c>
-      <c r="B27" s="83" t="s">
+      <c r="F27" s="84" t="s">
         <v>2355</v>
       </c>
-      <c r="C27" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D27" s="83" t="s">
-        <v>2108</v>
-      </c>
-      <c r="E27" s="84" t="s">
+      <c r="G27" s="84" t="s">
         <v>2356</v>
       </c>
-      <c r="F27" s="84" t="s">
+      <c r="H27" s="84" t="s">
         <v>2357</v>
       </c>
-      <c r="G27" s="84" t="s">
+      <c r="I27" s="83" t="s">
         <v>2358</v>
       </c>
-      <c r="H27" s="84" t="s">
+      <c r="J27" s="83" t="s">
         <v>2359</v>
       </c>
-      <c r="I27" s="83" t="s">
+      <c r="K27" s="84" t="s">
         <v>2360</v>
       </c>
-      <c r="J27" s="83" t="s">
+      <c r="L27" s="84" t="s">
+        <v>2191</v>
+      </c>
+      <c r="M27" s="84" t="s">
         <v>2361</v>
       </c>
-      <c r="K27" s="84" t="s">
+      <c r="N27" s="84" t="s">
         <v>2362</v>
-      </c>
-      <c r="L27" s="84" t="s">
-        <v>2193</v>
-      </c>
-      <c r="M27" s="84" t="s">
-        <v>2363</v>
-      </c>
-      <c r="N27" s="84" t="s">
-        <v>2364</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="83" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B28" s="83" t="s">
+        <v>2364</v>
+      </c>
+      <c r="C28" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D28" s="83" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E28" s="84" t="s">
         <v>2365</v>
       </c>
-      <c r="B28" s="83" t="s">
+      <c r="F28" s="84" t="s">
         <v>2366</v>
       </c>
-      <c r="C28" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D28" s="83" t="s">
-        <v>2108</v>
-      </c>
-      <c r="E28" s="84" t="s">
+      <c r="G28" s="84" t="s">
         <v>2367</v>
       </c>
-      <c r="F28" s="84" t="s">
+      <c r="H28" s="84" t="s">
         <v>2368</v>
       </c>
-      <c r="G28" s="84" t="s">
+      <c r="I28" s="83" t="s">
         <v>2369</v>
       </c>
-      <c r="H28" s="84" t="s">
+      <c r="J28" s="83" t="s">
         <v>2370</v>
       </c>
-      <c r="I28" s="83" t="s">
+      <c r="K28" s="84" t="s">
         <v>2371</v>
       </c>
-      <c r="J28" s="83" t="s">
+      <c r="L28" s="84" t="s">
+        <v>2169</v>
+      </c>
+      <c r="M28" s="84" t="s">
         <v>2372</v>
       </c>
-      <c r="K28" s="84" t="s">
+      <c r="N28" s="84" t="s">
         <v>2373</v>
-      </c>
-      <c r="L28" s="84" t="s">
-        <v>2171</v>
-      </c>
-      <c r="M28" s="84" t="s">
-        <v>2374</v>
-      </c>
-      <c r="N28" s="84" t="s">
-        <v>2375</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="83" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B29" s="83" t="s">
+        <v>2375</v>
+      </c>
+      <c r="C29" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D29" s="83" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E29" s="84" t="s">
         <v>2376</v>
       </c>
-      <c r="B29" s="83" t="s">
+      <c r="F29" s="84" t="s">
         <v>2377</v>
       </c>
-      <c r="C29" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D29" s="83" t="s">
-        <v>2108</v>
-      </c>
-      <c r="E29" s="84" t="s">
+      <c r="G29" s="84" t="s">
         <v>2378</v>
       </c>
-      <c r="F29" s="84" t="s">
+      <c r="H29" s="84" t="s">
         <v>2379</v>
       </c>
-      <c r="G29" s="84" t="s">
+      <c r="I29" s="83" t="s">
         <v>2380</v>
       </c>
-      <c r="H29" s="84" t="s">
+      <c r="J29" s="83" t="s">
         <v>2381</v>
       </c>
-      <c r="I29" s="83" t="s">
+      <c r="K29" s="84" t="s">
         <v>2382</v>
       </c>
-      <c r="J29" s="83" t="s">
+      <c r="L29" s="84" t="s">
         <v>2383</v>
       </c>
-      <c r="K29" s="84" t="s">
+      <c r="M29" s="84" t="s">
         <v>2384</v>
       </c>
-      <c r="L29" s="84" t="s">
+      <c r="N29" s="84" t="s">
         <v>2385</v>
-      </c>
-      <c r="M29" s="84" t="s">
-        <v>2386</v>
-      </c>
-      <c r="N29" s="84" t="s">
-        <v>2387</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="83" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B30" s="83" t="s">
+        <v>2387</v>
+      </c>
+      <c r="C30" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D30" s="83" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E30" s="84" t="s">
         <v>2388</v>
       </c>
-      <c r="B30" s="83" t="s">
+      <c r="F30" s="84" t="s">
         <v>2389</v>
       </c>
-      <c r="C30" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D30" s="83" t="s">
-        <v>2108</v>
-      </c>
-      <c r="E30" s="84" t="s">
+      <c r="G30" s="84" t="s">
         <v>2390</v>
       </c>
-      <c r="F30" s="84" t="s">
+      <c r="H30" s="84" t="s">
         <v>2391</v>
       </c>
-      <c r="G30" s="84" t="s">
+      <c r="I30" s="83" t="s">
         <v>2392</v>
       </c>
-      <c r="H30" s="84" t="s">
+      <c r="J30" s="83" t="s">
         <v>2393</v>
       </c>
-      <c r="I30" s="83" t="s">
+      <c r="K30" s="84" t="s">
         <v>2394</v>
       </c>
-      <c r="J30" s="83" t="s">
+      <c r="L30" s="84" t="s">
         <v>2395</v>
       </c>
-      <c r="K30" s="84" t="s">
+      <c r="M30" s="84" t="s">
         <v>2396</v>
       </c>
-      <c r="L30" s="84" t="s">
+      <c r="N30" s="84" t="s">
         <v>2397</v>
-      </c>
-      <c r="M30" s="84" t="s">
-        <v>2398</v>
-      </c>
-      <c r="N30" s="84" t="s">
-        <v>2399</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="83" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B31" s="83" t="s">
+        <v>2399</v>
+      </c>
+      <c r="C31" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D31" s="83" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E31" s="84" t="s">
         <v>2400</v>
       </c>
-      <c r="B31" s="83" t="s">
+      <c r="F31" s="84" t="s">
         <v>2401</v>
       </c>
-      <c r="C31" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="D31" s="83" t="s">
-        <v>2108</v>
-      </c>
-      <c r="E31" s="84" t="s">
+      <c r="G31" s="84" t="s">
         <v>2402</v>
       </c>
-      <c r="F31" s="84" t="s">
+      <c r="H31" s="84" t="s">
         <v>2403</v>
       </c>
-      <c r="G31" s="84" t="s">
+      <c r="I31" s="83" t="s">
         <v>2404</v>
       </c>
-      <c r="H31" s="84" t="s">
+      <c r="J31" s="83" t="s">
         <v>2405</v>
       </c>
-      <c r="I31" s="83" t="s">
+      <c r="K31" s="84" t="s">
         <v>2406</v>
       </c>
-      <c r="J31" s="83" t="s">
+      <c r="L31" s="84" t="s">
         <v>2407</v>
       </c>
-      <c r="K31" s="84" t="s">
+      <c r="M31" s="84" t="s">
         <v>2408</v>
       </c>
-      <c r="L31" s="84" t="s">
+      <c r="N31" s="84" t="s">
         <v>2409</v>
-      </c>
-      <c r="M31" s="84" t="s">
-        <v>2410</v>
-      </c>
-      <c r="N31" s="84" t="s">
-        <v>2411</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="83" t="s">
+        <v>2410</v>
+      </c>
+      <c r="B33" s="83" t="s">
+        <v>2411</v>
+      </c>
+      <c r="C33" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E33" s="84" t="s">
         <v>2412</v>
       </c>
-      <c r="B33" s="83" t="s">
+      <c r="F33" s="84" t="s">
         <v>2413</v>
       </c>
-      <c r="C33" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E33" s="84" t="s">
+      <c r="G33" s="84" t="s">
         <v>2414</v>
       </c>
-      <c r="F33" s="84" t="s">
+      <c r="H33" s="84" t="s">
         <v>2415</v>
-      </c>
-      <c r="G33" s="84" t="s">
-        <v>2416</v>
-      </c>
-      <c r="H33" s="84" t="s">
-        <v>2417</v>
       </c>
       <c r="I33" s="20" t="n">
         <v>1</v>
       </c>
       <c r="J33" s="83" t="s">
+        <v>2416</v>
+      </c>
+      <c r="K33" s="84" t="s">
+        <v>2417</v>
+      </c>
+      <c r="L33" s="84" t="s">
         <v>2418</v>
       </c>
-      <c r="K33" s="84" t="s">
+      <c r="M33" s="84" t="s">
         <v>2419</v>
       </c>
-      <c r="L33" s="84" t="s">
+      <c r="N33" s="84" t="s">
         <v>2420</v>
-      </c>
-      <c r="M33" s="84" t="s">
-        <v>2421</v>
-      </c>
-      <c r="N33" s="84" t="s">
-        <v>2422</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="83" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B34" s="83" t="s">
+        <v>2422</v>
+      </c>
+      <c r="C34" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E34" s="84" t="s">
         <v>2423</v>
       </c>
-      <c r="B34" s="83" t="s">
+      <c r="F34" s="84" t="s">
         <v>2424</v>
       </c>
-      <c r="C34" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E34" s="84" t="s">
+      <c r="G34" s="84" t="s">
         <v>2425</v>
       </c>
-      <c r="F34" s="84" t="s">
+      <c r="H34" s="84" t="s">
         <v>2426</v>
-      </c>
-      <c r="G34" s="84" t="s">
-        <v>2427</v>
-      </c>
-      <c r="H34" s="84" t="s">
-        <v>2428</v>
       </c>
       <c r="I34" s="20" t="n">
         <v>2</v>
       </c>
       <c r="J34" s="83" t="s">
+        <v>2427</v>
+      </c>
+      <c r="K34" s="84" t="s">
+        <v>2428</v>
+      </c>
+      <c r="L34" s="84" t="s">
         <v>2429</v>
       </c>
-      <c r="K34" s="84" t="s">
+      <c r="M34" s="84" t="s">
         <v>2430</v>
       </c>
-      <c r="L34" s="84" t="s">
+      <c r="N34" s="84" t="s">
         <v>2431</v>
-      </c>
-      <c r="M34" s="84" t="s">
-        <v>2432</v>
-      </c>
-      <c r="N34" s="84" t="s">
-        <v>2433</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="83" t="s">
+        <v>2432</v>
+      </c>
+      <c r="B35" s="83" t="s">
+        <v>2433</v>
+      </c>
+      <c r="C35" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E35" s="84" t="s">
         <v>2434</v>
       </c>
-      <c r="B35" s="83" t="s">
+      <c r="F35" s="84" t="s">
         <v>2435</v>
       </c>
-      <c r="C35" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E35" s="84" t="s">
+      <c r="G35" s="84" t="s">
         <v>2436</v>
       </c>
-      <c r="F35" s="84" t="s">
+      <c r="H35" s="84" t="s">
         <v>2437</v>
-      </c>
-      <c r="G35" s="84" t="s">
-        <v>2438</v>
-      </c>
-      <c r="H35" s="84" t="s">
-        <v>2439</v>
       </c>
       <c r="I35" s="20" t="n">
         <v>3</v>
       </c>
       <c r="J35" s="83" t="s">
+        <v>2438</v>
+      </c>
+      <c r="K35" s="84" t="s">
+        <v>2439</v>
+      </c>
+      <c r="L35" s="84" t="s">
         <v>2440</v>
       </c>
-      <c r="K35" s="84" t="s">
+      <c r="M35" s="84" t="s">
         <v>2441</v>
       </c>
-      <c r="L35" s="84" t="s">
+      <c r="N35" s="84" t="s">
         <v>2442</v>
-      </c>
-      <c r="M35" s="84" t="s">
-        <v>2443</v>
-      </c>
-      <c r="N35" s="84" t="s">
-        <v>2444</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -72943,542 +72941,542 @@
         <v>32</v>
       </c>
       <c r="B37" s="83" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C37" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="G37" s="84" t="s">
+        <v>2444</v>
+      </c>
+      <c r="H37" s="84" t="s">
+        <v>2444</v>
+      </c>
+      <c r="I37" s="83" t="s">
         <v>2445</v>
       </c>
-      <c r="C37" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="G37" s="84" t="s">
+      <c r="J37" s="83" t="s">
         <v>2446</v>
       </c>
-      <c r="H37" s="84" t="s">
-        <v>2446</v>
-      </c>
-      <c r="I37" s="83" t="s">
+      <c r="M37" s="84" t="s">
         <v>2447</v>
       </c>
-      <c r="J37" s="83" t="s">
+      <c r="N37" s="84" t="s">
         <v>2448</v>
-      </c>
-      <c r="M37" s="84" t="s">
-        <v>2449</v>
-      </c>
-      <c r="N37" s="84" t="s">
-        <v>2450</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="83" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="B38" s="83" t="s">
+        <v>2449</v>
+      </c>
+      <c r="C38" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E38" s="84" t="s">
+        <v>2450</v>
+      </c>
+      <c r="F38" s="84" t="s">
+        <v>2450</v>
+      </c>
+      <c r="G38" s="84" t="s">
         <v>2451</v>
       </c>
-      <c r="C38" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E38" s="84" t="s">
+      <c r="H38" s="84" t="s">
         <v>2452</v>
       </c>
-      <c r="F38" s="84" t="s">
-        <v>2452</v>
-      </c>
-      <c r="G38" s="84" t="s">
+      <c r="I38" s="83" t="s">
         <v>2453</v>
       </c>
-      <c r="H38" s="84" t="s">
+      <c r="J38" s="83" t="s">
         <v>2454</v>
       </c>
-      <c r="I38" s="83" t="s">
+      <c r="K38" s="84" t="s">
         <v>2455</v>
       </c>
-      <c r="J38" s="83" t="s">
+      <c r="L38" s="84" t="s">
+        <v>2455</v>
+      </c>
+      <c r="M38" s="84" t="s">
         <v>2456</v>
       </c>
-      <c r="K38" s="84" t="s">
+      <c r="N38" s="84" t="s">
         <v>2457</v>
-      </c>
-      <c r="L38" s="84" t="s">
-        <v>2457</v>
-      </c>
-      <c r="M38" s="84" t="s">
-        <v>2458</v>
-      </c>
-      <c r="N38" s="84" t="s">
-        <v>2459</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="83" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B39" s="83" t="s">
+        <v>2459</v>
+      </c>
+      <c r="C39" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E39" s="84" t="s">
         <v>2460</v>
       </c>
-      <c r="B39" s="83" t="s">
+      <c r="F39" s="84" t="s">
+        <v>2460</v>
+      </c>
+      <c r="G39" s="84" t="s">
         <v>2461</v>
       </c>
-      <c r="C39" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E39" s="84" t="s">
+      <c r="H39" s="84" t="s">
         <v>2462</v>
       </c>
-      <c r="F39" s="84" t="s">
-        <v>2462</v>
-      </c>
-      <c r="G39" s="84" t="s">
+      <c r="I39" s="83" t="s">
         <v>2463</v>
       </c>
-      <c r="H39" s="84" t="s">
+      <c r="J39" s="83" t="s">
         <v>2464</v>
       </c>
-      <c r="I39" s="83" t="s">
+      <c r="K39" s="84" t="s">
         <v>2465</v>
       </c>
-      <c r="J39" s="83" t="s">
+      <c r="L39" s="84" t="s">
+        <v>2465</v>
+      </c>
+      <c r="M39" s="84" t="s">
         <v>2466</v>
       </c>
-      <c r="K39" s="84" t="s">
+      <c r="N39" s="84" t="s">
         <v>2467</v>
-      </c>
-      <c r="L39" s="84" t="s">
-        <v>2467</v>
-      </c>
-      <c r="M39" s="84" t="s">
-        <v>2468</v>
-      </c>
-      <c r="N39" s="84" t="s">
-        <v>2469</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C40" s="83" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="83" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B41" s="83" t="s">
+        <v>2469</v>
+      </c>
+      <c r="C41" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E41" s="84" t="s">
         <v>2470</v>
       </c>
-      <c r="B41" s="83" t="s">
+      <c r="F41" s="84" t="s">
+        <v>2470</v>
+      </c>
+      <c r="G41" s="84" t="s">
         <v>2471</v>
       </c>
-      <c r="C41" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E41" s="84" t="s">
+      <c r="H41" s="84" t="s">
         <v>2472</v>
       </c>
-      <c r="F41" s="84" t="s">
-        <v>2472</v>
-      </c>
-      <c r="G41" s="84" t="s">
+      <c r="I41" s="83" t="s">
         <v>2473</v>
       </c>
-      <c r="H41" s="84" t="s">
+      <c r="J41" s="83" t="s">
         <v>2474</v>
       </c>
-      <c r="I41" s="83" t="s">
+      <c r="K41" s="84" t="s">
         <v>2475</v>
       </c>
-      <c r="J41" s="83" t="s">
+      <c r="M41" s="84" t="s">
         <v>2476</v>
       </c>
-      <c r="K41" s="84" t="s">
+      <c r="N41" s="84" t="s">
         <v>2477</v>
-      </c>
-      <c r="M41" s="84" t="s">
-        <v>2478</v>
-      </c>
-      <c r="N41" s="84" t="s">
-        <v>2479</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="83" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B42" s="83" t="s">
+        <v>2479</v>
+      </c>
+      <c r="C42" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E42" s="84" t="s">
         <v>2480</v>
       </c>
-      <c r="B42" s="83" t="s">
+      <c r="F42" s="84" t="s">
+        <v>2480</v>
+      </c>
+      <c r="G42" s="84" t="s">
         <v>2481</v>
       </c>
-      <c r="C42" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E42" s="84" t="s">
+      <c r="H42" s="84" t="s">
         <v>2482</v>
       </c>
-      <c r="F42" s="84" t="s">
-        <v>2482</v>
-      </c>
-      <c r="G42" s="84" t="s">
+      <c r="I42" s="83" t="s">
         <v>2483</v>
       </c>
-      <c r="H42" s="84" t="s">
+      <c r="J42" s="83" t="s">
         <v>2484</v>
       </c>
-      <c r="I42" s="83" t="s">
+      <c r="K42" s="84" t="s">
         <v>2485</v>
       </c>
-      <c r="J42" s="83" t="s">
+      <c r="L42" s="84" t="s">
         <v>2486</v>
       </c>
-      <c r="K42" s="84" t="s">
+      <c r="M42" s="84" t="s">
         <v>2487</v>
       </c>
-      <c r="L42" s="84" t="s">
+      <c r="N42" s="84" t="s">
         <v>2488</v>
-      </c>
-      <c r="M42" s="84" t="s">
-        <v>2489</v>
-      </c>
-      <c r="N42" s="84" t="s">
-        <v>2490</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="83" t="s">
+        <v>2489</v>
+      </c>
+      <c r="B43" s="83" t="s">
+        <v>2490</v>
+      </c>
+      <c r="C43" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E43" s="84" t="s">
         <v>2491</v>
       </c>
-      <c r="B43" s="83" t="s">
+      <c r="F43" s="84" t="s">
         <v>2492</v>
       </c>
-      <c r="C43" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E43" s="84" t="s">
+      <c r="G43" s="84" t="s">
         <v>2493</v>
       </c>
-      <c r="F43" s="84" t="s">
+      <c r="H43" s="84" t="s">
         <v>2494</v>
       </c>
-      <c r="G43" s="84" t="s">
+      <c r="I43" s="83" t="s">
         <v>2495</v>
       </c>
-      <c r="H43" s="84" t="s">
+      <c r="J43" s="83" t="s">
         <v>2496</v>
       </c>
-      <c r="I43" s="83" t="s">
+      <c r="M43" s="84" t="s">
         <v>2497</v>
       </c>
-      <c r="J43" s="83" t="s">
+      <c r="N43" s="84" t="s">
         <v>2498</v>
-      </c>
-      <c r="M43" s="84" t="s">
-        <v>2499</v>
-      </c>
-      <c r="N43" s="84" t="s">
-        <v>2500</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="83" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B44" s="83" t="s">
+        <v>2499</v>
+      </c>
+      <c r="C44" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E44" s="84" t="s">
+        <v>2500</v>
+      </c>
+      <c r="G44" s="84" t="s">
         <v>2501</v>
       </c>
-      <c r="B44" s="83" t="s">
+      <c r="H44" s="84" t="s">
         <v>2501</v>
       </c>
-      <c r="C44" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E44" s="84" t="s">
+      <c r="I44" s="83" t="s">
         <v>2502</v>
       </c>
-      <c r="G44" s="84" t="s">
+      <c r="J44" s="83" t="s">
         <v>2503</v>
       </c>
-      <c r="H44" s="84" t="s">
-        <v>2503</v>
-      </c>
-      <c r="I44" s="83" t="s">
+      <c r="K44" s="84" t="s">
         <v>2504</v>
       </c>
-      <c r="J44" s="83" t="s">
+      <c r="L44" s="84" t="s">
+        <v>2504</v>
+      </c>
+      <c r="M44" s="84" t="s">
         <v>2505</v>
       </c>
-      <c r="K44" s="84" t="s">
+      <c r="N44" s="84" t="s">
         <v>2506</v>
-      </c>
-      <c r="L44" s="84" t="s">
-        <v>2506</v>
-      </c>
-      <c r="M44" s="84" t="s">
-        <v>2507</v>
-      </c>
-      <c r="N44" s="84" t="s">
-        <v>2508</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="83" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B45" s="83" t="s">
+        <v>2508</v>
+      </c>
+      <c r="C45" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E45" s="84" t="s">
         <v>2509</v>
       </c>
-      <c r="B45" s="83" t="s">
+      <c r="F45" s="84" t="s">
         <v>2510</v>
       </c>
-      <c r="C45" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E45" s="84" t="s">
+      <c r="G45" s="84" t="s">
         <v>2511</v>
       </c>
-      <c r="F45" s="84" t="s">
+      <c r="H45" s="84" t="s">
         <v>2512</v>
       </c>
-      <c r="G45" s="84" t="s">
+      <c r="I45" s="83" t="s">
         <v>2513</v>
       </c>
-      <c r="H45" s="84" t="s">
+      <c r="J45" s="83" t="s">
         <v>2514</v>
       </c>
-      <c r="I45" s="83" t="s">
+      <c r="K45" s="84" t="s">
         <v>2515</v>
       </c>
-      <c r="J45" s="83" t="s">
+      <c r="L45" s="84" t="s">
+        <v>2515</v>
+      </c>
+      <c r="M45" s="84" t="s">
         <v>2516</v>
       </c>
-      <c r="K45" s="84" t="s">
+      <c r="N45" s="84" t="s">
         <v>2517</v>
-      </c>
-      <c r="L45" s="84" t="s">
-        <v>2517</v>
-      </c>
-      <c r="M45" s="84" t="s">
-        <v>2518</v>
-      </c>
-      <c r="N45" s="84" t="s">
-        <v>2519</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="83" t="s">
+        <v>2518</v>
+      </c>
+      <c r="B46" s="83" t="s">
+        <v>2518</v>
+      </c>
+      <c r="C46" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E46" s="84" t="s">
+        <v>2519</v>
+      </c>
+      <c r="F46" s="84" t="s">
+        <v>2519</v>
+      </c>
+      <c r="G46" s="84" t="s">
         <v>2520</v>
       </c>
-      <c r="B46" s="83" t="s">
-        <v>2520</v>
-      </c>
-      <c r="C46" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E46" s="84" t="s">
+      <c r="H46" s="84" t="s">
         <v>2521</v>
       </c>
-      <c r="F46" s="84" t="s">
-        <v>2521</v>
-      </c>
-      <c r="G46" s="84" t="s">
+      <c r="I46" s="83" t="s">
         <v>2522</v>
       </c>
-      <c r="H46" s="84" t="s">
+      <c r="J46" s="83" t="s">
         <v>2523</v>
       </c>
-      <c r="I46" s="83" t="s">
+      <c r="K46" s="84" t="s">
         <v>2524</v>
       </c>
-      <c r="J46" s="83" t="s">
+      <c r="L46" s="84" t="s">
+        <v>2524</v>
+      </c>
+      <c r="M46" s="84" t="s">
         <v>2525</v>
       </c>
-      <c r="K46" s="84" t="s">
+      <c r="N46" s="84" t="s">
         <v>2526</v>
-      </c>
-      <c r="L46" s="84" t="s">
-        <v>2526</v>
-      </c>
-      <c r="M46" s="84" t="s">
-        <v>2527</v>
-      </c>
-      <c r="N46" s="84" t="s">
-        <v>2528</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="83" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B47" s="83" t="s">
+        <v>2527</v>
+      </c>
+      <c r="C47" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E47" s="84" t="s">
+        <v>2528</v>
+      </c>
+      <c r="F47" s="84" t="s">
         <v>2529</v>
       </c>
-      <c r="B47" s="83" t="s">
-        <v>2529</v>
-      </c>
-      <c r="C47" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E47" s="84" t="s">
+      <c r="G47" s="84" t="s">
+        <v>2207</v>
+      </c>
+      <c r="H47" s="84" t="s">
         <v>2530</v>
       </c>
-      <c r="F47" s="84" t="s">
+      <c r="I47" s="83" t="s">
         <v>2531</v>
       </c>
-      <c r="G47" s="84" t="s">
-        <v>2209</v>
-      </c>
-      <c r="H47" s="84" t="s">
+      <c r="J47" s="83" t="s">
         <v>2532</v>
       </c>
-      <c r="I47" s="83" t="s">
+      <c r="K47" s="84" t="s">
         <v>2533</v>
       </c>
-      <c r="J47" s="83" t="s">
+      <c r="L47" s="84" t="s">
+        <v>2533</v>
+      </c>
+      <c r="M47" s="84" t="s">
+        <v>2212</v>
+      </c>
+      <c r="N47" s="84" t="s">
         <v>2534</v>
-      </c>
-      <c r="K47" s="84" t="s">
-        <v>2535</v>
-      </c>
-      <c r="L47" s="84" t="s">
-        <v>2535</v>
-      </c>
-      <c r="M47" s="84" t="s">
-        <v>2214</v>
-      </c>
-      <c r="N47" s="84" t="s">
-        <v>2536</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="83" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B48" s="83" t="s">
+        <v>2536</v>
+      </c>
+      <c r="C48" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E48" s="84" t="s">
         <v>2537</v>
       </c>
-      <c r="B48" s="83" t="s">
+      <c r="F48" s="84" t="s">
+        <v>2537</v>
+      </c>
+      <c r="G48" s="84" t="s">
         <v>2538</v>
       </c>
-      <c r="C48" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E48" s="84" t="s">
+      <c r="H48" s="84" t="s">
+        <v>2538</v>
+      </c>
+      <c r="I48" s="83" t="s">
         <v>2539</v>
       </c>
-      <c r="F48" s="84" t="s">
-        <v>2539</v>
-      </c>
-      <c r="G48" s="84" t="s">
+      <c r="J48" s="83" t="s">
         <v>2540</v>
       </c>
-      <c r="H48" s="84" t="s">
-        <v>2540</v>
-      </c>
-      <c r="I48" s="83" t="s">
+      <c r="K48" s="84" t="s">
         <v>2541</v>
       </c>
-      <c r="J48" s="83" t="s">
+      <c r="L48" s="84" t="s">
+        <v>2541</v>
+      </c>
+      <c r="M48" s="84" t="s">
         <v>2542</v>
       </c>
-      <c r="K48" s="84" t="s">
-        <v>2543</v>
-      </c>
-      <c r="L48" s="84" t="s">
-        <v>2543</v>
-      </c>
-      <c r="M48" s="84" t="s">
-        <v>2544</v>
-      </c>
       <c r="N48" s="84" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="83" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B49" s="83" t="s">
+        <v>2544</v>
+      </c>
+      <c r="C49" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E49" s="84" t="s">
         <v>2545</v>
       </c>
-      <c r="B49" s="83" t="s">
+      <c r="F49" s="84" t="s">
+        <v>2545</v>
+      </c>
+      <c r="G49" s="84" t="s">
+        <v>2471</v>
+      </c>
+      <c r="H49" s="84" t="s">
+        <v>2472</v>
+      </c>
+      <c r="I49" s="83" t="s">
         <v>2546</v>
       </c>
-      <c r="C49" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E49" s="84" t="s">
+      <c r="J49" s="83" t="s">
         <v>2547</v>
       </c>
-      <c r="F49" s="84" t="s">
-        <v>2547</v>
-      </c>
-      <c r="G49" s="84" t="s">
-        <v>2473</v>
-      </c>
-      <c r="H49" s="84" t="s">
-        <v>2474</v>
-      </c>
-      <c r="I49" s="83" t="s">
+      <c r="K49" s="84" t="s">
         <v>2548</v>
       </c>
-      <c r="J49" s="83" t="s">
+      <c r="L49" s="84" t="s">
+        <v>2548</v>
+      </c>
+      <c r="M49" s="84" t="s">
         <v>2549</v>
       </c>
-      <c r="K49" s="84" t="s">
+      <c r="N49" s="84" t="s">
         <v>2550</v>
-      </c>
-      <c r="L49" s="84" t="s">
-        <v>2550</v>
-      </c>
-      <c r="M49" s="84" t="s">
-        <v>2551</v>
-      </c>
-      <c r="N49" s="84" t="s">
-        <v>2552</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="83" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B50" s="83" t="s">
+        <v>2551</v>
+      </c>
+      <c r="C50" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="G50" s="84" t="s">
+        <v>2552</v>
+      </c>
+      <c r="H50" s="84" t="s">
+        <v>2552</v>
+      </c>
+      <c r="I50" s="83" t="s">
         <v>2553</v>
       </c>
-      <c r="B50" s="83" t="s">
+      <c r="J50" s="83" t="s">
         <v>2553</v>
       </c>
-      <c r="C50" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="G50" s="84" t="s">
+      <c r="M50" s="84" t="s">
         <v>2554</v>
       </c>
-      <c r="H50" s="84" t="s">
-        <v>2554</v>
-      </c>
-      <c r="I50" s="83" t="s">
+      <c r="N50" s="84" t="s">
         <v>2555</v>
-      </c>
-      <c r="J50" s="83" t="s">
-        <v>2555</v>
-      </c>
-      <c r="M50" s="84" t="s">
-        <v>2556</v>
-      </c>
-      <c r="N50" s="84" t="s">
-        <v>2557</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="83" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B51" s="83" t="s">
+        <v>2557</v>
+      </c>
+      <c r="C51" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E51" s="84" t="s">
         <v>2558</v>
       </c>
-      <c r="B51" s="83" t="s">
+      <c r="F51" s="84" t="s">
+        <v>2558</v>
+      </c>
+      <c r="G51" s="84" t="s">
         <v>2559</v>
       </c>
-      <c r="C51" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E51" s="84" t="s">
+      <c r="H51" s="84" t="s">
+        <v>2559</v>
+      </c>
+      <c r="I51" s="83" t="s">
         <v>2560</v>
       </c>
-      <c r="F51" s="84" t="s">
-        <v>2560</v>
-      </c>
-      <c r="G51" s="84" t="s">
+      <c r="J51" s="83" t="s">
         <v>2561</v>
       </c>
-      <c r="H51" s="84" t="s">
-        <v>2561</v>
-      </c>
-      <c r="I51" s="83" t="s">
+      <c r="K51" s="84" t="s">
         <v>2562</v>
       </c>
-      <c r="J51" s="83" t="s">
+      <c r="L51" s="84" t="s">
         <v>2563</v>
       </c>
-      <c r="K51" s="84" t="s">
+      <c r="M51" s="84" t="s">
         <v>2564</v>
       </c>
-      <c r="L51" s="84" t="s">
+      <c r="N51" s="84" t="s">
         <v>2565</v>
-      </c>
-      <c r="M51" s="84" t="s">
-        <v>2566</v>
-      </c>
-      <c r="N51" s="84" t="s">
-        <v>2567</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -73489,498 +73487,498 @@
         <v>2</v>
       </c>
       <c r="C52" s="83" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="E52" s="84" t="s">
+        <v>2566</v>
+      </c>
+      <c r="F52" s="84" t="s">
+        <v>2567</v>
+      </c>
+      <c r="G52" s="84" t="s">
         <v>2568</v>
       </c>
-      <c r="F52" s="84" t="s">
+      <c r="H52" s="84" t="s">
+        <v>2568</v>
+      </c>
+      <c r="I52" s="83" t="s">
         <v>2569</v>
       </c>
-      <c r="G52" s="84" t="s">
+      <c r="J52" s="83" t="s">
+        <v>2569</v>
+      </c>
+      <c r="K52" s="84" t="s">
         <v>2570</v>
       </c>
-      <c r="H52" s="84" t="s">
+      <c r="L52" s="84" t="s">
         <v>2570</v>
       </c>
-      <c r="I52" s="83" t="s">
+      <c r="M52" s="84" t="s">
         <v>2571</v>
       </c>
-      <c r="J52" s="83" t="s">
-        <v>2571</v>
-      </c>
-      <c r="K52" s="84" t="s">
+      <c r="N52" s="84" t="s">
         <v>2572</v>
-      </c>
-      <c r="L52" s="84" t="s">
-        <v>2572</v>
-      </c>
-      <c r="M52" s="84" t="s">
-        <v>2573</v>
-      </c>
-      <c r="N52" s="84" t="s">
-        <v>2574</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="83" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B53" s="83" t="s">
+        <v>2574</v>
+      </c>
+      <c r="C53" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="G53" s="84" t="s">
         <v>2575</v>
       </c>
-      <c r="B53" s="83" t="s">
+      <c r="H53" s="84" t="s">
         <v>2576</v>
       </c>
-      <c r="C53" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="G53" s="84" t="s">
+      <c r="I53" s="83" t="s">
         <v>2577</v>
       </c>
-      <c r="H53" s="84" t="s">
+      <c r="J53" s="83" t="s">
         <v>2578</v>
       </c>
-      <c r="I53" s="83" t="s">
+      <c r="K53" s="84" t="s">
         <v>2579</v>
       </c>
-      <c r="J53" s="83" t="s">
+      <c r="L53" s="84" t="s">
+        <v>2579</v>
+      </c>
+      <c r="M53" s="84" t="s">
         <v>2580</v>
       </c>
-      <c r="K53" s="84" t="s">
+      <c r="N53" s="84" t="s">
         <v>2581</v>
-      </c>
-      <c r="L53" s="84" t="s">
-        <v>2581</v>
-      </c>
-      <c r="M53" s="84" t="s">
-        <v>2582</v>
-      </c>
-      <c r="N53" s="84" t="s">
-        <v>2583</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="83" t="s">
+        <v>2582</v>
+      </c>
+      <c r="B54" s="83" t="s">
+        <v>2582</v>
+      </c>
+      <c r="C54" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E54" s="84" t="s">
+        <v>2216</v>
+      </c>
+      <c r="F54" s="84" t="s">
+        <v>2216</v>
+      </c>
+      <c r="G54" s="84" t="s">
+        <v>2583</v>
+      </c>
+      <c r="H54" s="84" t="s">
+        <v>2583</v>
+      </c>
+      <c r="I54" s="83" t="s">
         <v>2584</v>
       </c>
-      <c r="B54" s="83" t="s">
+      <c r="J54" s="83" t="s">
         <v>2584</v>
       </c>
-      <c r="C54" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E54" s="84" t="s">
-        <v>2218</v>
-      </c>
-      <c r="F54" s="84" t="s">
-        <v>2218</v>
-      </c>
-      <c r="G54" s="84" t="s">
+      <c r="K54" s="84" t="s">
         <v>2585</v>
       </c>
-      <c r="H54" s="84" t="s">
+      <c r="L54" s="84" t="s">
         <v>2585</v>
       </c>
-      <c r="I54" s="83" t="s">
+      <c r="M54" s="84" t="s">
         <v>2586</v>
       </c>
-      <c r="J54" s="83" t="s">
-        <v>2586</v>
-      </c>
-      <c r="K54" s="84" t="s">
+      <c r="N54" s="84" t="s">
         <v>2587</v>
-      </c>
-      <c r="L54" s="84" t="s">
-        <v>2587</v>
-      </c>
-      <c r="M54" s="84" t="s">
-        <v>2588</v>
-      </c>
-      <c r="N54" s="84" t="s">
-        <v>2589</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="83" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B55" s="83" t="s">
+        <v>2589</v>
+      </c>
+      <c r="C55" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E55" s="84" t="s">
         <v>2590</v>
       </c>
-      <c r="B55" s="83" t="s">
+      <c r="F55" s="84" t="s">
+        <v>2590</v>
+      </c>
+      <c r="G55" s="84" t="s">
         <v>2591</v>
       </c>
-      <c r="C55" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E55" s="84" t="s">
+      <c r="H55" s="84" t="s">
         <v>2592</v>
       </c>
-      <c r="F55" s="84" t="s">
-        <v>2592</v>
-      </c>
-      <c r="G55" s="84" t="s">
+      <c r="I55" s="83" t="s">
         <v>2593</v>
       </c>
-      <c r="H55" s="84" t="s">
+      <c r="J55" s="83" t="s">
         <v>2594</v>
       </c>
-      <c r="I55" s="83" t="s">
+      <c r="K55" s="84" t="s">
         <v>2595</v>
       </c>
-      <c r="J55" s="83" t="s">
+      <c r="L55" s="84" t="s">
+        <v>2595</v>
+      </c>
+      <c r="M55" s="84" t="s">
         <v>2596</v>
       </c>
-      <c r="K55" s="84" t="s">
-        <v>2597</v>
-      </c>
-      <c r="L55" s="84" t="s">
-        <v>2597</v>
-      </c>
-      <c r="M55" s="84" t="s">
-        <v>2598</v>
-      </c>
       <c r="N55" s="84" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="83" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B56" s="83" t="s">
+        <v>2597</v>
+      </c>
+      <c r="C56" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E56" s="84" t="s">
+        <v>2598</v>
+      </c>
+      <c r="F56" s="84" t="s">
+        <v>2598</v>
+      </c>
+      <c r="G56" s="84" t="s">
         <v>2599</v>
       </c>
-      <c r="B56" s="83" t="s">
-        <v>2599</v>
-      </c>
-      <c r="C56" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E56" s="84" t="s">
+      <c r="H56" s="84" t="s">
         <v>2600</v>
       </c>
-      <c r="F56" s="84" t="s">
-        <v>2600</v>
-      </c>
-      <c r="G56" s="84" t="s">
+      <c r="I56" s="83" t="s">
         <v>2601</v>
       </c>
-      <c r="H56" s="84" t="s">
+      <c r="J56" s="83" t="s">
         <v>2602</v>
       </c>
-      <c r="I56" s="83" t="s">
+      <c r="K56" s="84" t="s">
         <v>2603</v>
       </c>
-      <c r="J56" s="83" t="s">
+      <c r="L56" s="84" t="s">
+        <v>2603</v>
+      </c>
+      <c r="M56" s="84" t="s">
         <v>2604</v>
       </c>
-      <c r="K56" s="84" t="s">
+      <c r="N56" s="84" t="s">
         <v>2605</v>
-      </c>
-      <c r="L56" s="84" t="s">
-        <v>2605</v>
-      </c>
-      <c r="M56" s="84" t="s">
-        <v>2606</v>
-      </c>
-      <c r="N56" s="84" t="s">
-        <v>2607</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="83" t="s">
+        <v>2606</v>
+      </c>
+      <c r="B57" s="83" t="s">
+        <v>2607</v>
+      </c>
+      <c r="C57" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E57" s="84" t="s">
         <v>2608</v>
       </c>
-      <c r="B57" s="83" t="s">
+      <c r="F57" s="84" t="s">
+        <v>2608</v>
+      </c>
+      <c r="G57" s="84" t="s">
         <v>2609</v>
       </c>
-      <c r="C57" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E57" s="84" t="s">
+      <c r="H57" s="84" t="s">
         <v>2610</v>
       </c>
-      <c r="F57" s="84" t="s">
-        <v>2610</v>
-      </c>
-      <c r="G57" s="84" t="s">
+      <c r="I57" s="83" t="s">
         <v>2611</v>
       </c>
-      <c r="H57" s="84" t="s">
+      <c r="J57" s="83" t="s">
         <v>2612</v>
       </c>
-      <c r="I57" s="83" t="s">
+      <c r="K57" s="84" t="s">
         <v>2613</v>
       </c>
-      <c r="J57" s="83" t="s">
+      <c r="L57" s="84" t="s">
+        <v>2613</v>
+      </c>
+      <c r="M57" s="84" t="s">
         <v>2614</v>
       </c>
-      <c r="K57" s="84" t="s">
+      <c r="N57" s="84" t="s">
         <v>2615</v>
-      </c>
-      <c r="L57" s="84" t="s">
-        <v>2615</v>
-      </c>
-      <c r="M57" s="84" t="s">
-        <v>2616</v>
-      </c>
-      <c r="N57" s="84" t="s">
-        <v>2617</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="83" t="s">
+        <v>2616</v>
+      </c>
+      <c r="B58" s="83" t="s">
+        <v>2617</v>
+      </c>
+      <c r="C58" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E58" s="84" t="s">
         <v>2618</v>
       </c>
-      <c r="B58" s="83" t="s">
+      <c r="F58" s="84" t="s">
         <v>2619</v>
       </c>
-      <c r="C58" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E58" s="84" t="s">
+      <c r="G58" s="84" t="s">
         <v>2620</v>
       </c>
-      <c r="F58" s="84" t="s">
+      <c r="H58" s="84" t="s">
         <v>2621</v>
       </c>
-      <c r="G58" s="84" t="s">
+      <c r="I58" s="83" t="s">
         <v>2622</v>
       </c>
-      <c r="H58" s="84" t="s">
+      <c r="J58" s="83" t="s">
         <v>2623</v>
       </c>
-      <c r="I58" s="83" t="s">
+      <c r="K58" s="84" t="s">
         <v>2624</v>
       </c>
-      <c r="J58" s="83" t="s">
+      <c r="L58" s="84" t="s">
+        <v>2624</v>
+      </c>
+      <c r="M58" s="84" t="s">
         <v>2625</v>
       </c>
-      <c r="K58" s="84" t="s">
-        <v>2626</v>
-      </c>
-      <c r="L58" s="84" t="s">
-        <v>2626</v>
-      </c>
-      <c r="M58" s="84" t="s">
-        <v>2627</v>
-      </c>
       <c r="N58" s="84" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="83" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B59" s="83" t="s">
+        <v>2627</v>
+      </c>
+      <c r="C59" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="G59" s="84" t="s">
         <v>2628</v>
       </c>
-      <c r="B59" s="83" t="s">
+      <c r="H59" s="84" t="s">
         <v>2629</v>
       </c>
-      <c r="C59" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="G59" s="84" t="s">
+      <c r="I59" s="83" t="s">
         <v>2630</v>
       </c>
-      <c r="H59" s="84" t="s">
+      <c r="J59" s="83" t="s">
         <v>2631</v>
       </c>
-      <c r="I59" s="83" t="s">
+      <c r="K59" s="84" t="s">
         <v>2632</v>
       </c>
-      <c r="J59" s="83" t="s">
+      <c r="L59" s="84" t="s">
+        <v>2632</v>
+      </c>
+      <c r="M59" s="84" t="s">
         <v>2633</v>
       </c>
-      <c r="K59" s="84" t="s">
-        <v>2634</v>
-      </c>
-      <c r="L59" s="84" t="s">
-        <v>2634</v>
-      </c>
-      <c r="M59" s="84" t="s">
-        <v>2635</v>
-      </c>
       <c r="N59" s="84" t="s">
-        <v>2635</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="83" t="s">
+        <v>2634</v>
+      </c>
+      <c r="B60" s="83" t="s">
+        <v>2634</v>
+      </c>
+      <c r="C60" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E60" s="84" t="s">
+        <v>2635</v>
+      </c>
+      <c r="F60" s="84" t="s">
+        <v>2635</v>
+      </c>
+      <c r="G60" s="84" t="s">
         <v>2636</v>
       </c>
-      <c r="B60" s="83" t="s">
-        <v>2636</v>
-      </c>
-      <c r="C60" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E60" s="84" t="s">
+      <c r="H60" s="84" t="s">
         <v>2637</v>
       </c>
-      <c r="F60" s="84" t="s">
-        <v>2637</v>
-      </c>
-      <c r="G60" s="84" t="s">
+      <c r="I60" s="83" t="s">
         <v>2638</v>
       </c>
-      <c r="H60" s="84" t="s">
+      <c r="J60" s="83" t="s">
+        <v>2638</v>
+      </c>
+      <c r="K60" s="84" t="s">
         <v>2639</v>
       </c>
-      <c r="I60" s="83" t="s">
+      <c r="L60" s="84" t="s">
+        <v>2639</v>
+      </c>
+      <c r="M60" s="84" t="s">
         <v>2640</v>
       </c>
-      <c r="J60" s="83" t="s">
-        <v>2640</v>
-      </c>
-      <c r="K60" s="84" t="s">
+      <c r="N60" s="84" t="s">
         <v>2641</v>
-      </c>
-      <c r="L60" s="84" t="s">
-        <v>2641</v>
-      </c>
-      <c r="M60" s="84" t="s">
-        <v>2642</v>
-      </c>
-      <c r="N60" s="84" t="s">
-        <v>2643</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="83" t="s">
+        <v>2642</v>
+      </c>
+      <c r="B61" s="83" t="s">
+        <v>2642</v>
+      </c>
+      <c r="C61" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E61" s="84" t="s">
+        <v>2643</v>
+      </c>
+      <c r="F61" s="84" t="s">
+        <v>2643</v>
+      </c>
+      <c r="G61" s="84" t="s">
         <v>2644</v>
       </c>
-      <c r="B61" s="83" t="s">
+      <c r="H61" s="84" t="s">
         <v>2644</v>
       </c>
-      <c r="C61" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E61" s="84" t="s">
+      <c r="I61" s="83" t="s">
         <v>2645</v>
       </c>
-      <c r="F61" s="84" t="s">
+      <c r="J61" s="83" t="s">
         <v>2645</v>
       </c>
-      <c r="G61" s="84" t="s">
+      <c r="K61" s="84" t="s">
         <v>2646</v>
       </c>
-      <c r="H61" s="84" t="s">
+      <c r="L61" s="84" t="s">
         <v>2646</v>
       </c>
-      <c r="I61" s="83" t="s">
+      <c r="M61" s="84" t="s">
         <v>2647</v>
       </c>
-      <c r="J61" s="83" t="s">
+      <c r="N61" s="84" t="s">
         <v>2647</v>
-      </c>
-      <c r="K61" s="84" t="s">
-        <v>2648</v>
-      </c>
-      <c r="L61" s="84" t="s">
-        <v>2648</v>
-      </c>
-      <c r="M61" s="84" t="s">
-        <v>2649</v>
-      </c>
-      <c r="N61" s="84" t="s">
-        <v>2649</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="83" t="s">
+        <v>2648</v>
+      </c>
+      <c r="B62" s="83" t="s">
+        <v>2648</v>
+      </c>
+      <c r="C62" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E62" s="84" t="s">
+        <v>2649</v>
+      </c>
+      <c r="F62" s="84" t="s">
+        <v>2649</v>
+      </c>
+      <c r="G62" s="84" t="s">
         <v>2650</v>
       </c>
-      <c r="B62" s="83" t="s">
+      <c r="H62" s="84" t="s">
         <v>2650</v>
       </c>
-      <c r="C62" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E62" s="84" t="s">
+      <c r="I62" s="83" t="s">
         <v>2651</v>
       </c>
-      <c r="F62" s="84" t="s">
-        <v>2651</v>
-      </c>
-      <c r="G62" s="84" t="s">
+      <c r="J62" s="83" t="s">
         <v>2652</v>
       </c>
-      <c r="H62" s="84" t="s">
-        <v>2652</v>
-      </c>
-      <c r="I62" s="83" t="s">
+      <c r="K62" s="84" t="s">
         <v>2653</v>
       </c>
-      <c r="J62" s="83" t="s">
+      <c r="L62" s="84" t="s">
+        <v>2653</v>
+      </c>
+      <c r="M62" s="84" t="s">
         <v>2654</v>
       </c>
-      <c r="K62" s="84" t="s">
+      <c r="N62" s="84" t="s">
         <v>2655</v>
-      </c>
-      <c r="L62" s="84" t="s">
-        <v>2655</v>
-      </c>
-      <c r="M62" s="84" t="s">
-        <v>2656</v>
-      </c>
-      <c r="N62" s="84" t="s">
-        <v>2657</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="83" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B63" s="83" t="s">
+        <v>2657</v>
+      </c>
+      <c r="C63" s="83" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E63" s="84" t="s">
+        <v>2519</v>
+      </c>
+      <c r="F63" s="84" t="s">
+        <v>2519</v>
+      </c>
+      <c r="G63" s="84" t="s">
+        <v>2520</v>
+      </c>
+      <c r="H63" s="84" t="s">
+        <v>2521</v>
+      </c>
+      <c r="I63" s="83" t="s">
         <v>2658</v>
       </c>
-      <c r="B63" s="83" t="s">
+      <c r="J63" s="83" t="s">
         <v>2659</v>
       </c>
-      <c r="C63" s="83" t="s">
-        <v>2107</v>
-      </c>
-      <c r="E63" s="84" t="s">
-        <v>2521</v>
-      </c>
-      <c r="F63" s="84" t="s">
-        <v>2521</v>
-      </c>
-      <c r="G63" s="84" t="s">
-        <v>2522</v>
-      </c>
-      <c r="H63" s="84" t="s">
-        <v>2523</v>
-      </c>
-      <c r="I63" s="83" t="s">
-        <v>2660</v>
-      </c>
-      <c r="J63" s="83" t="s">
-        <v>2661</v>
-      </c>
       <c r="K63" s="84" t="s">
+        <v>2524</v>
+      </c>
+      <c r="L63" s="84" t="s">
+        <v>2524</v>
+      </c>
+      <c r="M63" s="84" t="s">
+        <v>2525</v>
+      </c>
+      <c r="N63" s="84" t="s">
         <v>2526</v>
-      </c>
-      <c r="L63" s="84" t="s">
-        <v>2526</v>
-      </c>
-      <c r="M63" s="84" t="s">
-        <v>2527</v>
-      </c>
-      <c r="N63" s="84" t="s">
-        <v>2528</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="83" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="B64" s="83" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="C64" s="83" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="83" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="B66" s="83" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="C66" s="83" t="s">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
   </sheetData>
@@ -74008,174 +74006,174 @@
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2"/>
       <c r="B1" s="85" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="C1" s="85" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="85" t="s">
-        <v>2115</v>
+        <v>2113</v>
       </c>
       <c r="B2" s="85" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="C2" s="85" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="85" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="B3" s="85" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="85" t="s">
-        <v>2113</v>
+        <v>2111</v>
       </c>
       <c r="B4" s="85" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="C4" s="85" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="85" t="s">
-        <v>2111</v>
+        <v>2109</v>
       </c>
       <c r="B5" s="85" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="C5" s="85" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="85" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="B6" s="85" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="C6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="85" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="B7" s="85" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="85" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="85" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="B9" s="85" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="C9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="85" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
       <c r="B10" s="85" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="85" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="C11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="85" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="C12" s="85" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="85" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="C13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="85" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
       <c r="C14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="85" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="C15" s="85" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="85" t="s">
-        <v>2117</v>
+        <v>2115</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="85" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
       <c r="B17" s="85" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="85" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
       <c r="B18" s="85" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
       <c r="C18" s="2"/>
     </row>

--- a/db/inflections/inflection_templates.xlsx
+++ b/db/inflections/inflection_templates.xlsx
@@ -5992,9 +5992,41 @@
 bhante</t>
   </si>
   <si>
-    <t xml:space="preserve">bhante
-bhonto
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Crimson Pro"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">bhante
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Crimson Pro"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">bho
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Crimson Pro"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">bhonto
 bhavanto</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">pokkharaṇi
@@ -9249,7 +9281,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -9361,6 +9393,13 @@
       <name val="Crimson Pro"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Crimson Pro"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -9902,7 +9941,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -44832,7 +44871,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="54.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="54.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
         <v>599</v>
       </c>
@@ -45056,7 +45095,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="54.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="54.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
         <v>630</v>
       </c>
@@ -57281,7 +57320,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="41" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="41.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="21" t="s">
         <v>420</v>
       </c>
@@ -58440,7 +58479,7 @@
       </c>
       <c r="DA120" s="47"/>
     </row>
-    <row r="121" customFormat="false" ht="42.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="54.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="21" t="s">
         <v>630</v>
       </c>
